--- a/optimized_version/metadata/testing_daily_metrics/agus5_testing_daily_metrics.xlsx
+++ b/optimized_version/metadata/testing_daily_metrics/agus5_testing_daily_metrics.xlsx
@@ -467,7 +467,7 @@
         <v>45757</v>
       </c>
       <c r="B2" t="n">
-        <v>5.972246594516338</v>
+        <v>6.229469435319766</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -476,10 +476,10 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>1.414478827938439</v>
+        <v>1.475400000000004</v>
       </c>
       <c r="F2" t="n">
-        <v>1.414478827938439</v>
+        <v>1.475400000000004</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
@@ -491,7 +491,7 @@
         <v>45758</v>
       </c>
       <c r="B3" t="n">
-        <v>4.042461925132291</v>
+        <v>4.047600616547579</v>
       </c>
       <c r="C3" t="n">
         <v>24</v>
@@ -500,13 +500,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8819499999999997</v>
+        <v>0.8851583333333325</v>
       </c>
       <c r="F3" t="n">
-        <v>1.092854093428875</v>
+        <v>1.061319185416589</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.5706195193809158</v>
+        <v>-0.4812850984198589</v>
       </c>
       <c r="H3" t="n">
         <v>24</v>
@@ -517,7 +517,7 @@
         <v>45759</v>
       </c>
       <c r="B4" t="n">
-        <v>4.403991565054852</v>
+        <v>4.14952581032333</v>
       </c>
       <c r="C4" t="n">
         <v>24</v>
@@ -526,13 +526,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9562302930153909</v>
+        <v>0.9013499999999998</v>
       </c>
       <c r="F4" t="n">
-        <v>1.198941507053559</v>
+        <v>1.115330435341921</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6545410866207968</v>
+        <v>-0.4318208161418917</v>
       </c>
       <c r="H4" t="n">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>45760</v>
       </c>
       <c r="B5" t="n">
-        <v>5.042796337837598</v>
+        <v>4.970894108663201</v>
       </c>
       <c r="C5" t="n">
         <v>24</v>
@@ -552,13 +552,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1.02843156899487</v>
+        <v>1.016020833333333</v>
       </c>
       <c r="F5" t="n">
-        <v>1.408804175080221</v>
+        <v>1.436149436137015</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3044702524680977</v>
+        <v>0.2772073736953518</v>
       </c>
       <c r="H5" t="n">
         <v>24</v>
@@ -569,7 +569,7 @@
         <v>45761</v>
       </c>
       <c r="B6" t="n">
-        <v>7.241208125938652</v>
+        <v>6.757077139445136</v>
       </c>
       <c r="C6" t="n">
         <v>24</v>
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1.668704166666667</v>
+        <v>1.558658333333333</v>
       </c>
       <c r="F6" t="n">
-        <v>2.410843342776956</v>
+        <v>2.278567447249843</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4536187240812275</v>
+        <v>-0.2984831075884948</v>
       </c>
       <c r="H6" t="n">
         <v>24</v>
@@ -595,7 +595,7 @@
         <v>45762</v>
       </c>
       <c r="B7" t="n">
-        <v>6.103701074521264</v>
+        <v>6.512622883374218</v>
       </c>
       <c r="C7" t="n">
         <v>24</v>
@@ -604,13 +604,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1.669666666666667</v>
+        <v>1.742954166666666</v>
       </c>
       <c r="F7" t="n">
-        <v>2.822862060805989</v>
+        <v>2.820536811975396</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8803966834847207</v>
+        <v>0.8805936416955624</v>
       </c>
       <c r="H7" t="n">
         <v>24</v>
@@ -621,7 +621,7 @@
         <v>45763</v>
       </c>
       <c r="B8" t="n">
-        <v>1.901622493580451</v>
+        <v>1.698499724237845</v>
       </c>
       <c r="C8" t="n">
         <v>24</v>
@@ -630,13 +630,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7639149023282034</v>
+        <v>0.6802151666666664</v>
       </c>
       <c r="F8" t="n">
-        <v>0.990969305495211</v>
+        <v>0.9163502385458286</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2174255042997029</v>
+        <v>0.330842609323037</v>
       </c>
       <c r="H8" t="n">
         <v>24</v>
@@ -647,7 +647,7 @@
         <v>45764</v>
       </c>
       <c r="B9" t="n">
-        <v>8.728701735076923</v>
+        <v>8.635196365992117</v>
       </c>
       <c r="C9" t="n">
         <v>24</v>
@@ -656,13 +656,13 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>2.296739264338463</v>
+        <v>2.275792416666665</v>
       </c>
       <c r="F9" t="n">
-        <v>3.528246172309463</v>
+        <v>3.544622690251647</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7387141584328597</v>
+        <v>0.7362829886445086</v>
       </c>
       <c r="H9" t="n">
         <v>24</v>
@@ -673,7 +673,7 @@
         <v>45765</v>
       </c>
       <c r="B10" t="n">
-        <v>11.36510100953686</v>
+        <v>10.98475140564851</v>
       </c>
       <c r="C10" t="n">
         <v>24</v>
@@ -682,13 +682,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>2.622748235661537</v>
+        <v>2.535483333333334</v>
       </c>
       <c r="F10" t="n">
-        <v>3.15252731644859</v>
+        <v>3.05201259632476</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.579277386473463</v>
+        <v>-1.417424822318435</v>
       </c>
       <c r="H10" t="n">
         <v>24</v>
@@ -699,7 +699,7 @@
         <v>45766</v>
       </c>
       <c r="B11" t="n">
-        <v>6.67234152229106</v>
+        <v>6.557511421894197</v>
       </c>
       <c r="C11" t="n">
         <v>24</v>
@@ -708,13 +708,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>1.612785097671797</v>
+        <v>1.589704166666666</v>
       </c>
       <c r="F11" t="n">
-        <v>1.944487807651032</v>
+        <v>1.948732994259773</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2391483722844665</v>
+        <v>-0.2445648714775179</v>
       </c>
       <c r="H11" t="n">
         <v>24</v>
@@ -725,7 +725,7 @@
         <v>45767</v>
       </c>
       <c r="B12" t="n">
-        <v>7.521319164886729</v>
+        <v>7.533961267058062</v>
       </c>
       <c r="C12" t="n">
         <v>24</v>
@@ -734,13 +734,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>2.174510735661537</v>
+        <v>2.1795875</v>
       </c>
       <c r="F12" t="n">
-        <v>2.665312987561137</v>
+        <v>2.70469905866007</v>
       </c>
       <c r="G12" t="n">
-        <v>0.393878143199065</v>
+        <v>0.3758321231975057</v>
       </c>
       <c r="H12" t="n">
         <v>24</v>
@@ -751,7 +751,7 @@
         <v>45768</v>
       </c>
       <c r="B13" t="n">
-        <v>6.09364370302215</v>
+        <v>6.109144702367782</v>
       </c>
       <c r="C13" t="n">
         <v>24</v>
@@ -760,13 +760,13 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>2.023488137989739</v>
+        <v>2.003676500000001</v>
       </c>
       <c r="F13" t="n">
-        <v>2.442179637151292</v>
+        <v>2.463149662131867</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7394757365475881</v>
+        <v>0.7349824917485427</v>
       </c>
       <c r="H13" t="n">
         <v>24</v>
@@ -777,7 +777,7 @@
         <v>45769</v>
       </c>
       <c r="B14" t="n">
-        <v>3.29990311337873</v>
+        <v>3.212501696482469</v>
       </c>
       <c r="C14" t="n">
         <v>24</v>
@@ -786,13 +786,13 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>1.32005656899487</v>
+        <v>1.289909666666666</v>
       </c>
       <c r="F14" t="n">
-        <v>1.826627988936276</v>
+        <v>1.703027188439417</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1026679029656949</v>
+        <v>0.04150979286548817</v>
       </c>
       <c r="H14" t="n">
         <v>24</v>
@@ -803,7 +803,7 @@
         <v>45770</v>
       </c>
       <c r="B15" t="n">
-        <v>5.075413300293311</v>
+        <v>4.376719955052394</v>
       </c>
       <c r="C15" t="n">
         <v>24</v>
@@ -812,13 +812,13 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>2.06024343100513</v>
+        <v>1.771614416744278</v>
       </c>
       <c r="F15" t="n">
-        <v>2.606807174210519</v>
+        <v>2.242043226919487</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.9662403818202567</v>
+        <v>-0.4544766693950106</v>
       </c>
       <c r="H15" t="n">
         <v>24</v>
@@ -829,7 +829,7 @@
         <v>45771</v>
       </c>
       <c r="B16" t="n">
-        <v>3.157178338141148</v>
+        <v>3.060486863661036</v>
       </c>
       <c r="C16" t="n">
         <v>24</v>
@@ -838,13 +838,13 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>1.325574362010261</v>
+        <v>1.295747333178116</v>
       </c>
       <c r="F16" t="n">
-        <v>1.589962688625425</v>
+        <v>1.583466397701449</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4687315479681895</v>
+        <v>0.4730640066051818</v>
       </c>
       <c r="H16" t="n">
         <v>24</v>
@@ -855,7 +855,7 @@
         <v>45772</v>
       </c>
       <c r="B17" t="n">
-        <v>3.324624287683434</v>
+        <v>2.969939848607591</v>
       </c>
       <c r="C17" t="n">
         <v>24</v>
@@ -864,13 +864,13 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1.428239264338461</v>
+        <v>1.28184583348855</v>
       </c>
       <c r="F17" t="n">
-        <v>1.68143074868867</v>
+        <v>1.568392274439458</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6365486607194897</v>
+        <v>-0.4239027915076514</v>
       </c>
       <c r="H17" t="n">
         <v>24</v>
@@ -881,7 +881,7 @@
         <v>45773</v>
       </c>
       <c r="B18" t="n">
-        <v>2.45704572451267</v>
+        <v>2.414463927666372</v>
       </c>
       <c r="C18" t="n">
         <v>24</v>
@@ -890,13 +890,13 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>1.029435735661538</v>
+        <v>1.016775750116418</v>
       </c>
       <c r="F18" t="n">
-        <v>1.422984169156716</v>
+        <v>1.330087245640455</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1450557036212257</v>
+        <v>-0.0004300662056293536</v>
       </c>
       <c r="H18" t="n">
         <v>24</v>
@@ -907,7 +907,7 @@
         <v>45774</v>
       </c>
       <c r="B19" t="n">
-        <v>7.006284664440493</v>
+        <v>7.169525542715014</v>
       </c>
       <c r="C19" t="n">
         <v>24</v>
@@ -916,13 +916,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>2.274183970896217</v>
+        <v>2.327360416511448</v>
       </c>
       <c r="F19" t="n">
-        <v>3.337460539335789</v>
+        <v>3.377298541889068</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6542148170314361</v>
+        <v>0.6459105349873684</v>
       </c>
       <c r="H19" t="n">
         <v>24</v>
@@ -933,7 +933,7 @@
         <v>45775</v>
       </c>
       <c r="B20" t="n">
-        <v>5.592713813040765</v>
+        <v>5.561154578385461</v>
       </c>
       <c r="C20" t="n">
         <v>24</v>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>2.125337500000002</v>
+        <v>2.089713833333338</v>
       </c>
       <c r="F20" t="n">
-        <v>2.577286201959498</v>
+        <v>2.649464920946874</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.008148180112239833</v>
+        <v>-0.06540669299836743</v>
       </c>
       <c r="H20" t="n">
         <v>24</v>
@@ -959,7 +959,7 @@
         <v>45776</v>
       </c>
       <c r="B21" t="n">
-        <v>4.470868231651443</v>
+        <v>4.205753056260541</v>
       </c>
       <c r="C21" t="n">
         <v>24</v>
@@ -968,13 +968,13 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>1.746058333333335</v>
+        <v>1.631178583488555</v>
       </c>
       <c r="F21" t="n">
-        <v>2.141843078585354</v>
+        <v>2.006726343537488</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2348981899510265</v>
+        <v>-0.08400718186835676</v>
       </c>
       <c r="H21" t="n">
         <v>24</v>
@@ -985,7 +985,7 @@
         <v>45777</v>
       </c>
       <c r="B22" t="n">
-        <v>4.345070425090134</v>
+        <v>3.744809449768428</v>
       </c>
       <c r="C22" t="n">
         <v>24</v>
@@ -994,13 +994,13 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>1.714899999999998</v>
+        <v>1.466188083333332</v>
       </c>
       <c r="F22" t="n">
-        <v>2.135865308414204</v>
+        <v>1.879323117944727</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3875208869776199</v>
+        <v>-0.07422367126692375</v>
       </c>
       <c r="H22" t="n">
         <v>24</v>
@@ -1011,7 +1011,7 @@
         <v>45778</v>
       </c>
       <c r="B23" t="n">
-        <v>4.456931304739483</v>
+        <v>4.657733511802264</v>
       </c>
       <c r="C23" t="n">
         <v>24</v>
@@ -1020,13 +1020,13 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>1.711610735661536</v>
+        <v>1.749225000116416</v>
       </c>
       <c r="F23" t="n">
-        <v>2.066620712434802</v>
+        <v>2.124432789711926</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4605663898273634</v>
+        <v>0.4299637968329321</v>
       </c>
       <c r="H23" t="n">
         <v>24</v>
@@ -1037,7 +1037,7 @@
         <v>45779</v>
       </c>
       <c r="B24" t="n">
-        <v>3.59641253199781</v>
+        <v>3.298443527213569</v>
       </c>
       <c r="C24" t="n">
         <v>24</v>
@@ -1046,13 +1046,13 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>1.492779166666667</v>
+        <v>1.371793166860694</v>
       </c>
       <c r="F24" t="n">
-        <v>2.285297276076679</v>
+        <v>2.053164398017423</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.091846618765502</v>
+        <v>-0.6884643031812745</v>
       </c>
       <c r="H24" t="n">
         <v>24</v>
@@ -1063,7 +1063,7 @@
         <v>45780</v>
       </c>
       <c r="B25" t="n">
-        <v>3.956966397819434</v>
+        <v>3.740742715376452</v>
       </c>
       <c r="C25" t="n">
         <v>24</v>
@@ -1072,13 +1072,13 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>1.6184875</v>
+        <v>1.51764375007761</v>
       </c>
       <c r="F25" t="n">
-        <v>1.92572723116383</v>
+        <v>1.79183705569869</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3042088403781038</v>
+        <v>0.3975980201945701</v>
       </c>
       <c r="H25" t="n">
         <v>24</v>
@@ -1089,7 +1089,7 @@
         <v>45781</v>
       </c>
       <c r="B26" t="n">
-        <v>3.116054884884622</v>
+        <v>3.192861136718187</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
@@ -1098,13 +1098,13 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>1.302135735661537</v>
+        <v>1.346418916783083</v>
       </c>
       <c r="F26" t="n">
-        <v>1.703846739642254</v>
+        <v>1.647891810245564</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.02725232730051808</v>
+        <v>0.03911045185882478</v>
       </c>
       <c r="H26" t="n">
         <v>24</v>
@@ -1115,7 +1115,7 @@
         <v>45782</v>
       </c>
       <c r="B27" t="n">
-        <v>1.982904004662247</v>
+        <v>2.249112793997005</v>
       </c>
       <c r="C27" t="n">
         <v>24</v>
@@ -1124,13 +1124,13 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0.8718732356615346</v>
+        <v>0.99631875085371</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9908467017880864</v>
+        <v>1.199859344240207</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.2332191306366389</v>
+        <v>-0.8083729124401959</v>
       </c>
       <c r="H27" t="n">
         <v>24</v>
@@ -1141,7 +1141,7 @@
         <v>45783</v>
       </c>
       <c r="B28" t="n">
-        <v>3.616517954029739</v>
+        <v>3.455122179725059</v>
       </c>
       <c r="C28" t="n">
         <v>24</v>
@@ -1150,13 +1150,13 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>1.506745833876605</v>
+        <v>1.449532762340024</v>
       </c>
       <c r="F28" t="n">
-        <v>2.059868604796609</v>
+        <v>1.868168637604633</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.8356063700065977</v>
+        <v>-0.5098460712478712</v>
       </c>
       <c r="H28" t="n">
         <v>24</v>
@@ -1167,7 +1167,7 @@
         <v>45784</v>
       </c>
       <c r="B29" t="n">
-        <v>3.941962586674033</v>
+        <v>3.397990121501965</v>
       </c>
       <c r="C29" t="n">
         <v>24</v>
@@ -1176,13 +1176,13 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>1.669514264338463</v>
+        <v>1.44057783376019</v>
       </c>
       <c r="F29" t="n">
-        <v>2.273669130366496</v>
+        <v>1.995634138941119</v>
       </c>
       <c r="G29" t="n">
-        <v>-1.476529669876475</v>
+        <v>-0.907879115387225</v>
       </c>
       <c r="H29" t="n">
         <v>24</v>
@@ -1193,7 +1193,7 @@
         <v>45785</v>
       </c>
       <c r="B30" t="n">
-        <v>3.254564911761752</v>
+        <v>3.338358895545156</v>
       </c>
       <c r="C30" t="n">
         <v>24</v>
@@ -1202,13 +1202,13 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>1.387650637989741</v>
+        <v>1.434915500232831</v>
       </c>
       <c r="F30" t="n">
-        <v>1.608445199706638</v>
+        <v>1.640436629495938</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.2700406378965989</v>
+        <v>-0.3210644197499433</v>
       </c>
       <c r="H30" t="n">
         <v>24</v>
@@ -1219,7 +1219,7 @@
         <v>45786</v>
       </c>
       <c r="B31" t="n">
-        <v>2.876496198134795</v>
+        <v>2.681473995527007</v>
       </c>
       <c r="C31" t="n">
         <v>24</v>
@@ -1228,13 +1228,13 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>1.240989264338464</v>
+        <v>1.162599999805975</v>
       </c>
       <c r="F31" t="n">
-        <v>1.507962296473523</v>
+        <v>1.456186861188088</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3644823602073277</v>
+        <v>0.4073737833199289</v>
       </c>
       <c r="H31" t="n">
         <v>24</v>
@@ -1245,7 +1245,7 @@
         <v>45787</v>
       </c>
       <c r="B32" t="n">
-        <v>3.249298051371404</v>
+        <v>3.049258358261771</v>
       </c>
       <c r="C32" t="n">
         <v>24</v>
@@ -1254,13 +1254,13 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>1.350898235661537</v>
+        <v>1.270360583682582</v>
       </c>
       <c r="F32" t="n">
-        <v>1.550429846060382</v>
+        <v>1.455886960988094</v>
       </c>
       <c r="G32" t="n">
-        <v>-1.366526340665854</v>
+        <v>-1.086711529660468</v>
       </c>
       <c r="H32" t="n">
         <v>24</v>
@@ -1271,7 +1271,7 @@
         <v>45788</v>
       </c>
       <c r="B33" t="n">
-        <v>3.890719998577954</v>
+        <v>3.736277134940089</v>
       </c>
       <c r="C33" t="n">
         <v>24</v>
@@ -1280,13 +1280,13 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>1.58176970698461</v>
+        <v>1.523643166511447</v>
       </c>
       <c r="F33" t="n">
-        <v>2.001747662157137</v>
+        <v>1.875857690786727</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1199204363113172</v>
+        <v>0.2271360454776921</v>
       </c>
       <c r="H33" t="n">
         <v>24</v>
@@ -1297,7 +1297,7 @@
         <v>45789</v>
       </c>
       <c r="B34" t="n">
-        <v>8.101250485668908</v>
+        <v>7.849023122630666</v>
       </c>
       <c r="C34" t="n">
         <v>24</v>
@@ -1306,13 +1306,13 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>2.937607695343595</v>
+        <v>2.822860416821888</v>
       </c>
       <c r="F34" t="n">
-        <v>4.237660342791185</v>
+        <v>4.283873624369394</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5879478623358159</v>
+        <v>0.5789116907040472</v>
       </c>
       <c r="H34" t="n">
         <v>24</v>
@@ -1323,7 +1323,7 @@
         <v>45790</v>
       </c>
       <c r="B35" t="n">
-        <v>3.586835230330812</v>
+        <v>3.149425500310383</v>
       </c>
       <c r="C35" t="n">
         <v>24</v>
@@ -1332,13 +1332,13 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>1.555057695343595</v>
+        <v>1.377426500543271</v>
       </c>
       <c r="F35" t="n">
-        <v>1.927085823162622</v>
+        <v>1.809257311884996</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.0143363220001147</v>
+        <v>0.1059114417678823</v>
       </c>
       <c r="H35" t="n">
         <v>24</v>
@@ -1349,7 +1349,7 @@
         <v>45791</v>
       </c>
       <c r="B36" t="n">
-        <v>3.753573325419645</v>
+        <v>3.45605416093562</v>
       </c>
       <c r="C36" t="n">
         <v>24</v>
@@ -1358,13 +1358,13 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>1.575837068994868</v>
+        <v>1.460902249961195</v>
       </c>
       <c r="F36" t="n">
-        <v>1.809677151158719</v>
+        <v>1.676219129104035</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.3017951367080938</v>
+        <v>-0.1168684521342345</v>
       </c>
       <c r="H36" t="n">
         <v>24</v>
@@ -1375,7 +1375,7 @@
         <v>45792</v>
       </c>
       <c r="B37" t="n">
-        <v>0.1937180079152678</v>
+        <v>0.712101450020208</v>
       </c>
       <c r="C37" t="n">
         <v>24</v>
@@ -1384,13 +1384,13 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>0.08245317206156244</v>
+        <v>0.3048325826348404</v>
       </c>
       <c r="F37" t="n">
-        <v>0.08245317206156244</v>
+        <v>0.3678399234151236</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9832121638923403</v>
+        <v>0.6658836629153579</v>
       </c>
       <c r="H37" t="n">
         <v>24</v>
@@ -1401,7 +1401,7 @@
         <v>45793</v>
       </c>
       <c r="B38" t="n">
-        <v>2.811848151266931</v>
+        <v>2.746126919028864</v>
       </c>
       <c r="C38" t="n">
         <v>24</v>
@@ -1410,13 +1410,13 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>1.204473235661536</v>
+        <v>1.187393749961194</v>
       </c>
       <c r="F38" t="n">
-        <v>1.413300519480429</v>
+        <v>1.424373981505397</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.4523095269266051</v>
+        <v>-0.4751568933763162</v>
       </c>
       <c r="H38" t="n">
         <v>24</v>
@@ -1427,7 +1427,7 @@
         <v>45794</v>
       </c>
       <c r="B39" t="n">
-        <v>4.163225512511275</v>
+        <v>4.06115985269515</v>
       </c>
       <c r="C39" t="n">
         <v>24</v>
@@ -1436,13 +1436,13 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>1.816254804656404</v>
+        <v>1.78657441662786</v>
       </c>
       <c r="F39" t="n">
-        <v>2.180551338975548</v>
+        <v>2.106958318675141</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.2138109959542744</v>
+        <v>-0.1332619921895082</v>
       </c>
       <c r="H39" t="n">
         <v>24</v>
@@ -1453,7 +1453,7 @@
         <v>45795</v>
       </c>
       <c r="B40" t="n">
-        <v>3.141819867871702</v>
+        <v>3.227041053248969</v>
       </c>
       <c r="C40" t="n">
         <v>24</v>
@@ -1462,13 +1462,13 @@
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>1.374633333333335</v>
+        <v>1.42481250031044</v>
       </c>
       <c r="F40" t="n">
-        <v>1.682787070510054</v>
+        <v>1.739479506537115</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.184107625409322</v>
+        <v>-1.333750022551819</v>
       </c>
       <c r="H40" t="n">
         <v>24</v>
@@ -1479,7 +1479,7 @@
         <v>45796</v>
       </c>
       <c r="B41" t="n">
-        <v>3.839060652123685</v>
+        <v>3.994794829564805</v>
       </c>
       <c r="C41" t="n">
         <v>24</v>
@@ -1488,13 +1488,13 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>1.628283333333333</v>
+        <v>1.712629166821888</v>
       </c>
       <c r="F41" t="n">
-        <v>1.952995761615185</v>
+        <v>1.979136210986455</v>
       </c>
       <c r="G41" t="n">
-        <v>0.1040317811370676</v>
+        <v>0.0798865627429558</v>
       </c>
       <c r="H41" t="n">
         <v>24</v>
@@ -1505,7 +1505,7 @@
         <v>45797</v>
       </c>
       <c r="B42" t="n">
-        <v>3.248750362566311</v>
+        <v>3.789011195801179</v>
       </c>
       <c r="C42" t="n">
         <v>24</v>
@@ -1514,13 +1514,13 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>1.457054166666666</v>
+        <v>1.7161187492239</v>
       </c>
       <c r="F42" t="n">
-        <v>2.195239038223587</v>
+        <v>2.254396588770756</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.2173198556576228</v>
+        <v>-0.2838128213642896</v>
       </c>
       <c r="H42" t="n">
         <v>24</v>
@@ -1531,7 +1531,7 @@
         <v>45798</v>
       </c>
       <c r="B43" t="n">
-        <v>3.153845538684258</v>
+        <v>3.03033487049331</v>
       </c>
       <c r="C43" t="n">
         <v>24</v>
@@ -1540,13 +1540,13 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>1.393547597671799</v>
+        <v>1.352481250077611</v>
       </c>
       <c r="F43" t="n">
-        <v>1.677247882116142</v>
+        <v>1.720805376652226</v>
       </c>
       <c r="G43" t="n">
-        <v>-1.042845650900231</v>
+        <v>-1.150327250760731</v>
       </c>
       <c r="H43" t="n">
         <v>24</v>
@@ -1557,7 +1557,7 @@
         <v>45799</v>
       </c>
       <c r="B44" t="n">
-        <v>2.730758851814582</v>
+        <v>2.67464525457971</v>
       </c>
       <c r="C44" t="n">
         <v>24</v>
@@ -1566,13 +1566,13 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>1.175585735661536</v>
+        <v>1.161245250194025</v>
       </c>
       <c r="F44" t="n">
-        <v>1.395457449458945</v>
+        <v>1.377597574744319</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.09367159464737984</v>
+        <v>-0.06585585384096371</v>
       </c>
       <c r="H44" t="n">
         <v>24</v>
@@ -1583,7 +1583,7 @@
         <v>45800</v>
       </c>
       <c r="B45" t="n">
-        <v>5.522841075672727</v>
+        <v>4.999729283904869</v>
       </c>
       <c r="C45" t="n">
         <v>24</v>
@@ -1592,13 +1592,13 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>2.277012500000002</v>
+        <v>2.065521000232834</v>
       </c>
       <c r="F45" t="n">
-        <v>2.677050328978714</v>
+        <v>2.43489212206066</v>
       </c>
       <c r="G45" t="n">
-        <v>-1.224957267496337</v>
+        <v>-0.8406365908188866</v>
       </c>
       <c r="H45" t="n">
         <v>24</v>
@@ -1609,7 +1609,7 @@
         <v>45801</v>
       </c>
       <c r="B46" t="n">
-        <v>4.854018167319072</v>
+        <v>4.438819012156921</v>
       </c>
       <c r="C46" t="n">
         <v>24</v>
@@ -1618,13 +1618,13 @@
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>2.053097597671797</v>
+        <v>1.891240500232833</v>
       </c>
       <c r="F46" t="n">
-        <v>2.39684238234805</v>
+        <v>2.237150300167296</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.9371500403259838</v>
+        <v>-0.6876198854737627</v>
       </c>
       <c r="H46" t="n">
         <v>24</v>
@@ -1635,7 +1635,7 @@
         <v>45802</v>
       </c>
       <c r="B47" t="n">
-        <v>6.123529789694569</v>
+        <v>5.684404392470622</v>
       </c>
       <c r="C47" t="n">
         <v>24</v>
@@ -1644,13 +1644,13 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>2.38415</v>
+        <v>2.205309666821886</v>
       </c>
       <c r="F47" t="n">
-        <v>3.178248080707995</v>
+        <v>2.956259995492076</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.2931600349144143</v>
+        <v>-0.1188244291237506</v>
       </c>
       <c r="H47" t="n">
         <v>24</v>
@@ -1661,7 +1661,7 @@
         <v>45803</v>
       </c>
       <c r="B48" t="n">
-        <v>2.993417494656845</v>
+        <v>2.691036921813511</v>
       </c>
       <c r="C48" t="n">
         <v>24</v>
@@ -1670,13 +1670,13 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>1.266243431005129</v>
+        <v>1.143541999999999</v>
       </c>
       <c r="F48" t="n">
-        <v>1.777462211273343</v>
+        <v>1.625276046223975</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.5899888116873433</v>
+        <v>-0.3293752372814294</v>
       </c>
       <c r="H48" t="n">
         <v>24</v>
@@ -1687,7 +1687,7 @@
         <v>45804</v>
       </c>
       <c r="B49" t="n">
-        <v>6.029839921659879</v>
+        <v>5.257908897509555</v>
       </c>
       <c r="C49" t="n">
         <v>24</v>
@@ -1696,13 +1696,13 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>2.457468431005131</v>
+        <v>2.14442633344975</v>
       </c>
       <c r="F49" t="n">
-        <v>2.93809604578484</v>
+        <v>2.524535826456853</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.3642421743995461</v>
+        <v>-0.007215894135151446</v>
       </c>
       <c r="H49" t="n">
         <v>24</v>
@@ -1713,7 +1713,7 @@
         <v>45805</v>
       </c>
       <c r="B50" t="n">
-        <v>3.584055619871434</v>
+        <v>3.792575222710973</v>
       </c>
       <c r="C50" t="n">
         <v>24</v>
@@ -1722,13 +1722,13 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>1.580479166666665</v>
+        <v>1.69794241577415</v>
       </c>
       <c r="F50" t="n">
-        <v>2.458127981476654</v>
+        <v>2.40299511686207</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.2474667642692259</v>
+        <v>-0.1921359349197274</v>
       </c>
       <c r="H50" t="n">
         <v>24</v>
@@ -1739,7 +1739,7 @@
         <v>45806</v>
       </c>
       <c r="B51" t="n">
-        <v>3.799767425160125</v>
+        <v>3.844634052445678</v>
       </c>
       <c r="C51" t="n">
         <v>24</v>
@@ -1748,13 +1748,13 @@
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>1.554051764338464</v>
+        <v>1.612011749301512</v>
       </c>
       <c r="F51" t="n">
-        <v>2.261369254216398</v>
+        <v>2.119150693320071</v>
       </c>
       <c r="G51" t="n">
-        <v>0.6751188338484013</v>
+        <v>0.7146977148202296</v>
       </c>
       <c r="H51" t="n">
         <v>24</v>
@@ -1765,7 +1765,7 @@
         <v>45807</v>
       </c>
       <c r="B52" t="n">
-        <v>2.406065753077734</v>
+        <v>2.542933628983521</v>
       </c>
       <c r="C52" t="n">
         <v>24</v>
@@ -1774,13 +1774,13 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>1.045768431005129</v>
+        <v>1.123252082867675</v>
       </c>
       <c r="F52" t="n">
-        <v>1.522207592269326</v>
+        <v>1.505777661630401</v>
       </c>
       <c r="G52" t="n">
-        <v>0.7090751299984888</v>
+        <v>0.7153214260928658</v>
       </c>
       <c r="H52" t="n">
         <v>24</v>
@@ -1791,7 +1791,7 @@
         <v>45808</v>
       </c>
       <c r="B53" t="n">
-        <v>2.53802006264537</v>
+        <v>3.035613665392785</v>
       </c>
       <c r="C53" t="n">
         <v>24</v>
@@ -1800,13 +1800,13 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>1.105786373651277</v>
+        <v>1.351214582440821</v>
       </c>
       <c r="F53" t="n">
-        <v>1.589015832309377</v>
+        <v>1.68284685915204</v>
       </c>
       <c r="G53" t="n">
-        <v>0.5818447710189678</v>
+        <v>0.5310027715377914</v>
       </c>
       <c r="H53" t="n">
         <v>24</v>
@@ -1817,7 +1817,7 @@
         <v>45809</v>
       </c>
       <c r="B54" t="n">
-        <v>1.94932372358601</v>
+        <v>2.248782432805489</v>
       </c>
       <c r="C54" t="n">
         <v>24</v>
@@ -1826,13 +1826,13 @@
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>0.8525357357779511</v>
+        <v>1.003691666278616</v>
       </c>
       <c r="F54" t="n">
-        <v>1.165333006159501</v>
+        <v>1.288591776195979</v>
       </c>
       <c r="G54" t="n">
-        <v>0.7371340890989162</v>
+        <v>0.6785859290874059</v>
       </c>
       <c r="H54" t="n">
         <v>24</v>
@@ -1843,7 +1843,7 @@
         <v>45810</v>
       </c>
       <c r="B55" t="n">
-        <v>3.562497551255108</v>
+        <v>3.950046108941902</v>
       </c>
       <c r="C55" t="n">
         <v>24</v>
@@ -1852,13 +1852,13 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>1.469971471323072</v>
+        <v>1.67053808275126</v>
       </c>
       <c r="F55" t="n">
-        <v>2.736261986562344</v>
+        <v>2.616333310608777</v>
       </c>
       <c r="G55" t="n">
-        <v>0.328418500503507</v>
+        <v>0.3859983886448896</v>
       </c>
       <c r="H55" t="n">
         <v>24</v>
@@ -1869,7 +1869,7 @@
         <v>45811</v>
       </c>
       <c r="B56" t="n">
-        <v>1.735762815868554</v>
+        <v>2.343189482735182</v>
       </c>
       <c r="C56" t="n">
         <v>24</v>
@@ -1878,13 +1878,13 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0.7576054426461459</v>
+        <v>1.05641874875824</v>
       </c>
       <c r="F56" t="n">
-        <v>1.318967889918762</v>
+        <v>1.411791836444903</v>
       </c>
       <c r="G56" t="n">
-        <v>0.7706040917412712</v>
+        <v>0.7371799134180734</v>
       </c>
       <c r="H56" t="n">
         <v>24</v>
@@ -1895,7 +1895,7 @@
         <v>45812</v>
       </c>
       <c r="B57" t="n">
-        <v>3.674007205197594</v>
+        <v>3.446326577719761</v>
       </c>
       <c r="C57" t="n">
         <v>24</v>
@@ -1904,13 +1904,13 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>1.501773724020522</v>
+        <v>1.431085416239813</v>
       </c>
       <c r="F57" t="n">
-        <v>2.415649857205938</v>
+        <v>2.1446801755452</v>
       </c>
       <c r="G57" t="n">
-        <v>0.5008642005183092</v>
+        <v>0.6065624331896491</v>
       </c>
       <c r="H57" t="n">
         <v>24</v>
@@ -1921,7 +1921,7 @@
         <v>45813</v>
       </c>
       <c r="B58" t="n">
-        <v>3.280055349192608</v>
+        <v>3.877524772609743</v>
       </c>
       <c r="C58" t="n">
         <v>24</v>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>1.390554166666666</v>
+        <v>1.671592416589058</v>
       </c>
       <c r="F58" t="n">
-        <v>1.996341078572715</v>
+        <v>2.030504022166203</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.04594099628186776</v>
+        <v>-0.08204521131330345</v>
       </c>
       <c r="H58" t="n">
         <v>24</v>
@@ -1947,7 +1947,7 @@
         <v>45814</v>
       </c>
       <c r="B59" t="n">
-        <v>2.424911348330693</v>
+        <v>2.583490267100641</v>
       </c>
       <c r="C59" t="n">
         <v>24</v>
@@ -1956,13 +1956,13 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>1.047173235661538</v>
+        <v>1.130961332790067</v>
       </c>
       <c r="F59" t="n">
-        <v>1.672831411722288</v>
+        <v>1.607627512830821</v>
       </c>
       <c r="G59" t="n">
-        <v>0.5027458077107785</v>
+        <v>0.5407544427055493</v>
       </c>
       <c r="H59" t="n">
         <v>24</v>
@@ -1973,7 +1973,7 @@
         <v>45815</v>
       </c>
       <c r="B60" t="n">
-        <v>2.00850009751085</v>
+        <v>2.550764282265684</v>
       </c>
       <c r="C60" t="n">
         <v>24</v>
@@ -1982,13 +1982,13 @@
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>0.9144225976717953</v>
+        <v>1.174383332324404</v>
       </c>
       <c r="F60" t="n">
-        <v>1.266632072065659</v>
+        <v>1.451517040417554</v>
       </c>
       <c r="G60" t="n">
-        <v>0.017012385844697</v>
+        <v>-0.2908963180272712</v>
       </c>
       <c r="H60" t="n">
         <v>24</v>
@@ -1999,7 +1999,7 @@
         <v>45816</v>
       </c>
       <c r="B61" t="n">
-        <v>3.619944239214541</v>
+        <v>3.816670513550593</v>
       </c>
       <c r="C61" t="n">
         <v>24</v>
@@ -2008,13 +2008,13 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>1.521242304656407</v>
+        <v>1.626454916395035</v>
       </c>
       <c r="F61" t="n">
-        <v>2.05077491645184</v>
+        <v>2.012245473782427</v>
       </c>
       <c r="G61" t="n">
-        <v>0.4860562981443988</v>
+        <v>0.5051865762441405</v>
       </c>
       <c r="H61" t="n">
         <v>24</v>
@@ -2025,7 +2025,7 @@
         <v>45817</v>
       </c>
       <c r="B62" t="n">
-        <v>3.122977236307689</v>
+        <v>3.124114888382463</v>
       </c>
       <c r="C62" t="n">
         <v>24</v>
@@ -2034,13 +2034,13 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>1.336476126348725</v>
+        <v>1.36068141596818</v>
       </c>
       <c r="F62" t="n">
-        <v>1.804776828889354</v>
+        <v>1.707834458215035</v>
       </c>
       <c r="G62" t="n">
-        <v>0.5678113597859138</v>
+        <v>0.6129938395721088</v>
       </c>
       <c r="H62" t="n">
         <v>24</v>
@@ -2051,7 +2051,7 @@
         <v>45818</v>
       </c>
       <c r="B63" t="n">
-        <v>2.850479098464636</v>
+        <v>3.154841190278717</v>
       </c>
       <c r="C63" t="n">
         <v>24</v>
@@ -2060,13 +2060,13 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>1.27958093100513</v>
+        <v>1.436940332557236</v>
       </c>
       <c r="F63" t="n">
-        <v>1.914846110848581</v>
+        <v>1.940816747335347</v>
       </c>
       <c r="G63" t="n">
-        <v>0.1575412764226923</v>
+        <v>0.1345341423711915</v>
       </c>
       <c r="H63" t="n">
         <v>24</v>
@@ -2077,7 +2077,7 @@
         <v>45819</v>
       </c>
       <c r="B64" t="n">
-        <v>4.325849303768203</v>
+        <v>4.289962916939861</v>
       </c>
       <c r="C64" t="n">
         <v>24</v>
@@ -2086,13 +2086,13 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>1.889669068994871</v>
+        <v>1.891943749456731</v>
       </c>
       <c r="F64" t="n">
-        <v>3.236466115168936</v>
+        <v>2.884685613321142</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.1398751162678953</v>
+        <v>0.09445065383577356</v>
       </c>
       <c r="H64" t="n">
         <v>24</v>
@@ -2103,7 +2103,7 @@
         <v>45820</v>
       </c>
       <c r="B65" t="n">
-        <v>3.74515907752532</v>
+        <v>3.388303572477569</v>
       </c>
       <c r="C65" t="n">
         <v>24</v>
@@ -2112,13 +2112,13 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>1.571821471323073</v>
+        <v>1.439485416278617</v>
       </c>
       <c r="F65" t="n">
-        <v>2.425715251983233</v>
+        <v>2.164905384785881</v>
       </c>
       <c r="G65" t="n">
-        <v>0.5649530233326807</v>
+        <v>0.6534751705604259</v>
       </c>
       <c r="H65" t="n">
         <v>24</v>
@@ -2129,7 +2129,7 @@
         <v>45821</v>
       </c>
       <c r="B66" t="n">
-        <v>4.936607015533443</v>
+        <v>5.113066326172429</v>
       </c>
       <c r="C66" t="n">
         <v>24</v>
@@ -2138,13 +2138,13 @@
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>2.023305442646146</v>
+        <v>2.151686166084595</v>
       </c>
       <c r="F66" t="n">
-        <v>2.808528130907665</v>
+        <v>2.696412952373367</v>
       </c>
       <c r="G66" t="n">
-        <v>0.4322020189972807</v>
+        <v>0.4766296724473474</v>
       </c>
       <c r="H66" t="n">
         <v>24</v>
@@ -2155,7 +2155,7 @@
         <v>45822</v>
       </c>
       <c r="B67" t="n">
-        <v>2.693820693226623</v>
+        <v>2.676482024062425</v>
       </c>
       <c r="C67" t="n">
         <v>24</v>
@@ -2164,13 +2164,13 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>1.142901126348723</v>
+        <v>1.146672916278617</v>
       </c>
       <c r="F67" t="n">
-        <v>1.917392598615959</v>
+        <v>1.807599626928957</v>
       </c>
       <c r="G67" t="n">
-        <v>0.6794014629368206</v>
+        <v>0.7150662268663841</v>
       </c>
       <c r="H67" t="n">
         <v>24</v>
@@ -2181,7 +2181,7 @@
         <v>45823</v>
       </c>
       <c r="B68" t="n">
-        <v>2.635231576586987</v>
+        <v>3.109612900984841</v>
       </c>
       <c r="C68" t="n">
         <v>24</v>
@@ -2190,13 +2190,13 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>1.136628040317943</v>
+        <v>1.368422916045789</v>
       </c>
       <c r="F68" t="n">
-        <v>1.698771913263934</v>
+        <v>1.755686141973096</v>
       </c>
       <c r="G68" t="n">
-        <v>0.6804093547270147</v>
+        <v>0.6586360328306869</v>
       </c>
       <c r="H68" t="n">
         <v>24</v>
@@ -2207,7 +2207,7 @@
         <v>45824</v>
       </c>
       <c r="B69" t="n">
-        <v>4.925992091955004</v>
+        <v>4.665148134802552</v>
       </c>
       <c r="C69" t="n">
         <v>24</v>
@@ -2216,13 +2216,13 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>1.970302402328202</v>
+        <v>1.904828999379121</v>
       </c>
       <c r="F69" t="n">
-        <v>2.676589054608419</v>
+        <v>2.528640042763177</v>
       </c>
       <c r="G69" t="n">
-        <v>0.6415008472115378</v>
+        <v>0.6800377365617346</v>
       </c>
       <c r="H69" t="n">
         <v>24</v>
@@ -2233,7 +2233,7 @@
         <v>45825</v>
       </c>
       <c r="B70" t="n">
-        <v>2.642057765950738</v>
+        <v>2.938680818298977</v>
       </c>
       <c r="C70" t="n">
         <v>24</v>
@@ -2242,13 +2242,13 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>1.131491666666668</v>
+        <v>1.282595999301514</v>
       </c>
       <c r="F70" t="n">
-        <v>1.810134202101473</v>
+        <v>1.803539315226413</v>
       </c>
       <c r="G70" t="n">
-        <v>0.5489823331299171</v>
+        <v>0.552262744198726</v>
       </c>
       <c r="H70" t="n">
         <v>24</v>
@@ -2259,7 +2259,7 @@
         <v>45826</v>
       </c>
       <c r="B71" t="n">
-        <v>2.277613636752013</v>
+        <v>2.815695807750537</v>
       </c>
       <c r="C71" t="n">
         <v>24</v>
@@ -2268,13 +2268,13 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>0.9661890949743487</v>
+        <v>1.226936915968178</v>
       </c>
       <c r="F71" t="n">
-        <v>1.572245616714263</v>
+        <v>1.547251240330954</v>
       </c>
       <c r="G71" t="n">
-        <v>0.6265798676087148</v>
+        <v>0.6383581998643441</v>
       </c>
       <c r="H71" t="n">
         <v>24</v>
@@ -2285,7 +2285,7 @@
         <v>45827</v>
       </c>
       <c r="B72" t="n">
-        <v>3.20397180701223</v>
+        <v>3.613865684614574</v>
       </c>
       <c r="C72" t="n">
         <v>24</v>
@@ -2294,13 +2294,13 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>1.381567623651275</v>
+        <v>1.593881999650756</v>
       </c>
       <c r="F72" t="n">
-        <v>2.120396829401409</v>
+        <v>2.089474414888858</v>
       </c>
       <c r="G72" t="n">
-        <v>0.3409742655212339</v>
+        <v>0.3600556680188063</v>
       </c>
       <c r="H72" t="n">
         <v>24</v>
@@ -2311,7 +2311,7 @@
         <v>45828</v>
       </c>
       <c r="B73" t="n">
-        <v>3.578101430708618</v>
+        <v>3.24681395013473</v>
       </c>
       <c r="C73" t="n">
         <v>24</v>
@@ -2320,13 +2320,13 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1.469416666666666</v>
+        <v>1.365552665968178</v>
       </c>
       <c r="F73" t="n">
-        <v>2.102426431276094</v>
+        <v>1.936373037630922</v>
       </c>
       <c r="G73" t="n">
-        <v>0.6945535582975499</v>
+        <v>0.7408975567347098</v>
       </c>
       <c r="H73" t="n">
         <v>24</v>
@@ -2337,7 +2337,7 @@
         <v>45829</v>
       </c>
       <c r="B74" t="n">
-        <v>6.86380541346773</v>
+        <v>7.414968456734903</v>
       </c>
       <c r="C74" t="n">
         <v>24</v>
@@ -2346,13 +2346,13 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>2.621797597671798</v>
+        <v>2.847137499689563</v>
       </c>
       <c r="F74" t="n">
-        <v>4.458693106666209</v>
+        <v>4.621517510034995</v>
       </c>
       <c r="G74" t="n">
-        <v>0.4145133348203822</v>
+        <v>0.3709704434191688</v>
       </c>
       <c r="H74" t="n">
         <v>24</v>
@@ -2363,7 +2363,7 @@
         <v>45830</v>
       </c>
       <c r="B75" t="n">
-        <v>9.332672259953229</v>
+        <v>9.384137202864846</v>
       </c>
       <c r="C75" t="n">
         <v>24</v>
@@ -2372,13 +2372,13 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>3.230994706984609</v>
+        <v>3.299495832906479</v>
       </c>
       <c r="F75" t="n">
-        <v>5.567405811554338</v>
+        <v>5.485396758321698</v>
       </c>
       <c r="G75" t="n">
-        <v>0.5065420107096755</v>
+        <v>0.5209724196467396</v>
       </c>
       <c r="H75" t="n">
         <v>24</v>
@@ -2389,7 +2389,7 @@
         <v>45831</v>
       </c>
       <c r="B76" t="n">
-        <v>4.901025688092417</v>
+        <v>4.183049434951469</v>
       </c>
       <c r="C76" t="n">
         <v>24</v>
@@ -2398,13 +2398,13 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>2.018693431005131</v>
+        <v>1.72015358344975</v>
       </c>
       <c r="F76" t="n">
-        <v>2.631976854877141</v>
+        <v>2.297726890483353</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.9325265110029983</v>
+        <v>-0.4728487226228679</v>
       </c>
       <c r="H76" t="n">
         <v>24</v>
@@ -2415,7 +2415,7 @@
         <v>45832</v>
       </c>
       <c r="B77" t="n">
-        <v>4.439813351568645</v>
+        <v>4.07610299372744</v>
       </c>
       <c r="C77" t="n">
         <v>24</v>
@@ -2424,13 +2424,13 @@
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>1.822462499999999</v>
+        <v>1.674434833333334</v>
       </c>
       <c r="F77" t="n">
-        <v>2.308502660479369</v>
+        <v>2.019787905021384</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.2741750440716875</v>
+        <v>0.02460647024503804</v>
       </c>
       <c r="H77" t="n">
         <v>24</v>
@@ -2441,7 +2441,7 @@
         <v>45833</v>
       </c>
       <c r="B78" t="n">
-        <v>2.060410877848764</v>
+        <v>2.662588982170119</v>
       </c>
       <c r="C78" t="n">
         <v>24</v>
@@ -2450,13 +2450,13 @@
         <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>0.9472208333333336</v>
+        <v>1.236083332246796</v>
       </c>
       <c r="F78" t="n">
-        <v>1.251510165416918</v>
+        <v>1.548207577236941</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.5196957188210649</v>
+        <v>-1.325660165640291</v>
       </c>
       <c r="H78" t="n">
         <v>24</v>
@@ -2467,7 +2467,7 @@
         <v>45834</v>
       </c>
       <c r="B79" t="n">
-        <v>1.968866699760896</v>
+        <v>2.360160228877306</v>
       </c>
       <c r="C79" t="n">
         <v>24</v>
@@ -2476,13 +2476,13 @@
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>0.8632624999999988</v>
+        <v>1.050512498991068</v>
       </c>
       <c r="F79" t="n">
-        <v>1.437054998602308</v>
+        <v>1.516987205149978</v>
       </c>
       <c r="G79" t="n">
-        <v>0.4084017552871095</v>
+        <v>0.3407594196440576</v>
       </c>
       <c r="H79" t="n">
         <v>24</v>
@@ -2493,7 +2493,7 @@
         <v>45835</v>
       </c>
       <c r="B80" t="n">
-        <v>3.717400309838407</v>
+        <v>4.006033310928208</v>
       </c>
       <c r="C80" t="n">
         <v>24</v>
@@ -2502,13 +2502,13 @@
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>1.58238220698461</v>
+        <v>1.733126500116415</v>
       </c>
       <c r="F80" t="n">
-        <v>2.221735260456053</v>
+        <v>2.186716121377954</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.0316487799969507</v>
+        <v>0.0006167478468468435</v>
       </c>
       <c r="H80" t="n">
         <v>24</v>
@@ -2519,7 +2519,7 @@
         <v>45836</v>
       </c>
       <c r="B81" t="n">
-        <v>2.721121319162147</v>
+        <v>3.036631675124819</v>
       </c>
       <c r="C81" t="n">
         <v>24</v>
@@ -2528,13 +2528,13 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>1.177873235661538</v>
+        <v>1.330958332984089</v>
       </c>
       <c r="F81" t="n">
-        <v>1.601795057289238</v>
+        <v>1.629178236756921</v>
       </c>
       <c r="G81" t="n">
-        <v>0.3267075318854734</v>
+        <v>0.3034904785609573</v>
       </c>
       <c r="H81" t="n">
         <v>24</v>
@@ -2545,7 +2545,7 @@
         <v>45837</v>
       </c>
       <c r="B82" t="n">
-        <v>2.375923756708413</v>
+        <v>3.104774915803854</v>
       </c>
       <c r="C82" t="n">
         <v>24</v>
@@ -2554,13 +2554,13 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>1.067536373651274</v>
+        <v>1.410358332634843</v>
       </c>
       <c r="F82" t="n">
-        <v>1.686655995442312</v>
+        <v>1.764518794401635</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.1818447488429629</v>
+        <v>-0.2934807747489876</v>
       </c>
       <c r="H82" t="n">
         <v>24</v>
@@ -2571,7 +2571,7 @@
         <v>45838</v>
       </c>
       <c r="B83" t="n">
-        <v>4.475063071370143</v>
+        <v>3.818746560884607</v>
       </c>
       <c r="C83" t="n">
         <v>23</v>
@@ -2580,13 +2580,13 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>1.888400920524416</v>
+        <v>1.610600782608698</v>
       </c>
       <c r="F83" t="n">
-        <v>2.740444782548174</v>
+        <v>2.561816290986406</v>
       </c>
       <c r="G83" t="n">
-        <v>0.4544871328379902</v>
+        <v>0.5232849605693957</v>
       </c>
       <c r="H83" t="n">
         <v>23</v>

--- a/optimized_version/metadata/testing_daily_metrics/agus5_testing_daily_metrics.xlsx
+++ b/optimized_version/metadata/testing_daily_metrics/agus5_testing_daily_metrics.xlsx
@@ -467,7 +467,7 @@
         <v>45757</v>
       </c>
       <c r="B2" t="n">
-        <v>6.229469435319766</v>
+        <v>4.63832428369971</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -476,10 +476,10 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>1.475400000000004</v>
+        <v>1.098550000000007</v>
       </c>
       <c r="F2" t="n">
-        <v>1.475400000000004</v>
+        <v>1.098550000000007</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
@@ -491,7 +491,7 @@
         <v>45758</v>
       </c>
       <c r="B3" t="n">
-        <v>4.047600616547579</v>
+        <v>4.054359490969071</v>
       </c>
       <c r="C3" t="n">
         <v>24</v>
@@ -500,13 +500,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8851583333333325</v>
+        <v>0.885533332984087</v>
       </c>
       <c r="F3" t="n">
-        <v>1.061319185416589</v>
+        <v>1.053623660260273</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.4812850984198589</v>
+        <v>-0.4598816612795793</v>
       </c>
       <c r="H3" t="n">
         <v>24</v>
@@ -517,7 +517,7 @@
         <v>45759</v>
       </c>
       <c r="B4" t="n">
-        <v>4.14952581032333</v>
+        <v>4.281038009641805</v>
       </c>
       <c r="C4" t="n">
         <v>24</v>
@@ -526,13 +526,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9013499999999998</v>
+        <v>0.9312083328288683</v>
       </c>
       <c r="F4" t="n">
-        <v>1.115330435341921</v>
+        <v>1.126474038171817</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.4318208161418917</v>
+        <v>-0.4605752566363583</v>
       </c>
       <c r="H4" t="n">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>45760</v>
       </c>
       <c r="B5" t="n">
-        <v>4.970894108663201</v>
+        <v>5.277309409175917</v>
       </c>
       <c r="C5" t="n">
         <v>24</v>
@@ -552,13 +552,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1.016020833333333</v>
+        <v>1.08881666631742</v>
       </c>
       <c r="F5" t="n">
-        <v>1.436149436137015</v>
+        <v>1.428542002183876</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2772073736953518</v>
+        <v>0.2848445090880097</v>
       </c>
       <c r="H5" t="n">
         <v>24</v>
@@ -569,7 +569,7 @@
         <v>45761</v>
       </c>
       <c r="B6" t="n">
-        <v>6.757077139445136</v>
+        <v>7.029248332954853</v>
       </c>
       <c r="C6" t="n">
         <v>24</v>
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1.558658333333333</v>
+        <v>1.616626499495534</v>
       </c>
       <c r="F6" t="n">
-        <v>2.278567447249843</v>
+        <v>2.297455527522284</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2984831075884948</v>
+        <v>-0.3200997651645896</v>
       </c>
       <c r="H6" t="n">
         <v>24</v>
@@ -595,7 +595,7 @@
         <v>45762</v>
       </c>
       <c r="B7" t="n">
-        <v>6.512622883374218</v>
+        <v>6.732832566500793</v>
       </c>
       <c r="C7" t="n">
         <v>24</v>
@@ -604,13 +604,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1.742954166666666</v>
+        <v>1.814813999650752</v>
       </c>
       <c r="F7" t="n">
-        <v>2.820536811975396</v>
+        <v>2.809228179731139</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8805936416955624</v>
+        <v>0.8815492155444695</v>
       </c>
       <c r="H7" t="n">
         <v>24</v>
@@ -621,7 +621,7 @@
         <v>45763</v>
       </c>
       <c r="B8" t="n">
-        <v>1.698499724237845</v>
+        <v>1.876086906352101</v>
       </c>
       <c r="C8" t="n">
         <v>24</v>
@@ -630,13 +630,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6802151666666664</v>
+        <v>0.7540166661621986</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9163502385458286</v>
+        <v>0.9968018460793026</v>
       </c>
       <c r="G8" t="n">
-        <v>0.330842609323037</v>
+        <v>0.2081864092018251</v>
       </c>
       <c r="H8" t="n">
         <v>24</v>
@@ -647,7 +647,7 @@
         <v>45764</v>
       </c>
       <c r="B9" t="n">
-        <v>8.635196365992117</v>
+        <v>8.590510103481728</v>
       </c>
       <c r="C9" t="n">
         <v>24</v>
@@ -656,13 +656,13 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>2.275792416666665</v>
+        <v>2.28745491631742</v>
       </c>
       <c r="F9" t="n">
-        <v>3.544622690251647</v>
+        <v>3.522763901192981</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7362829886445086</v>
+        <v>0.7395255116510198</v>
       </c>
       <c r="H9" t="n">
         <v>24</v>
@@ -673,7 +673,7 @@
         <v>45765</v>
       </c>
       <c r="B10" t="n">
-        <v>10.98475140564851</v>
+        <v>10.33510781732629</v>
       </c>
       <c r="C10" t="n">
         <v>24</v>
@@ -682,13 +682,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>2.535483333333334</v>
+        <v>2.384200000349246</v>
       </c>
       <c r="F10" t="n">
-        <v>3.05201259632476</v>
+        <v>2.928461372959143</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.417424822318435</v>
+        <v>-1.225662629103912</v>
       </c>
       <c r="H10" t="n">
         <v>24</v>
@@ -699,7 +699,7 @@
         <v>45766</v>
       </c>
       <c r="B11" t="n">
-        <v>6.557511421894197</v>
+        <v>6.415960866307353</v>
       </c>
       <c r="C11" t="n">
         <v>24</v>
@@ -708,13 +708,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>1.589704166666666</v>
+        <v>1.555006832828867</v>
       </c>
       <c r="F11" t="n">
-        <v>1.948732994259773</v>
+        <v>1.887752507544083</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2445648714775179</v>
+        <v>-0.1678927800901941</v>
       </c>
       <c r="H11" t="n">
         <v>24</v>
@@ -725,7 +725,7 @@
         <v>45767</v>
       </c>
       <c r="B12" t="n">
-        <v>7.533961267058062</v>
+        <v>7.636165254731313</v>
       </c>
       <c r="C12" t="n">
         <v>24</v>
@@ -734,13 +734,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>2.1795875</v>
+        <v>2.208030666317421</v>
       </c>
       <c r="F12" t="n">
-        <v>2.70469905866007</v>
+        <v>2.702221388521715</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3758321231975057</v>
+        <v>0.3769751514900754</v>
       </c>
       <c r="H12" t="n">
         <v>24</v>
@@ -751,7 +751,7 @@
         <v>45768</v>
       </c>
       <c r="B13" t="n">
-        <v>6.109144702367782</v>
+        <v>6.136846046289083</v>
       </c>
       <c r="C13" t="n">
         <v>24</v>
@@ -760,13 +760,13 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>2.003676500000001</v>
+        <v>2.002797333837799</v>
       </c>
       <c r="F13" t="n">
-        <v>2.463149662131867</v>
+        <v>2.479212714394238</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7349824917485427</v>
+        <v>0.7315146791306573</v>
       </c>
       <c r="H13" t="n">
         <v>24</v>
@@ -777,7 +777,7 @@
         <v>45769</v>
       </c>
       <c r="B14" t="n">
-        <v>3.212501696482469</v>
+        <v>3.129545264337455</v>
       </c>
       <c r="C14" t="n">
         <v>24</v>
@@ -786,13 +786,13 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>1.289909666666666</v>
+        <v>1.255241499495532</v>
       </c>
       <c r="F14" t="n">
-        <v>1.703027188439417</v>
+        <v>1.694767747423859</v>
       </c>
       <c r="G14" t="n">
-        <v>0.04150979286548817</v>
+        <v>0.05078433199721699</v>
       </c>
       <c r="H14" t="n">
         <v>24</v>
@@ -803,7 +803,7 @@
         <v>45770</v>
       </c>
       <c r="B15" t="n">
-        <v>4.376719955052394</v>
+        <v>4.194201229155587</v>
       </c>
       <c r="C15" t="n">
         <v>24</v>
@@ -812,13 +812,13 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>1.771614416744278</v>
+        <v>1.692337916162201</v>
       </c>
       <c r="F15" t="n">
-        <v>2.242043226919487</v>
+        <v>2.192079193755643</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4544766693950106</v>
+        <v>-0.3903728415589247</v>
       </c>
       <c r="H15" t="n">
         <v>24</v>
@@ -829,7 +829,7 @@
         <v>45771</v>
       </c>
       <c r="B16" t="n">
-        <v>3.060486863661036</v>
+        <v>2.994908878201462</v>
       </c>
       <c r="C16" t="n">
         <v>24</v>
@@ -838,13 +838,13 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>1.295747333178116</v>
+        <v>1.262926499495539</v>
       </c>
       <c r="F16" t="n">
-        <v>1.583466397701449</v>
+        <v>1.59300829040739</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4730640066051818</v>
+        <v>0.4666942903137076</v>
       </c>
       <c r="H16" t="n">
         <v>24</v>
@@ -855,7 +855,7 @@
         <v>45772</v>
       </c>
       <c r="B17" t="n">
-        <v>2.969939848607591</v>
+        <v>2.915920794172641</v>
       </c>
       <c r="C17" t="n">
         <v>24</v>
@@ -864,13 +864,13 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1.28184583348855</v>
+        <v>1.257066666317416</v>
       </c>
       <c r="F17" t="n">
-        <v>1.568392274439458</v>
+        <v>1.55213857346228</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4239027915076514</v>
+        <v>-0.3945430857701329</v>
       </c>
       <c r="H17" t="n">
         <v>24</v>
@@ -881,7 +881,7 @@
         <v>45773</v>
       </c>
       <c r="B18" t="n">
-        <v>2.414463927666372</v>
+        <v>2.445416515372999</v>
       </c>
       <c r="C18" t="n">
         <v>24</v>
@@ -890,13 +890,13 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>1.016775750116418</v>
+        <v>1.031042416162201</v>
       </c>
       <c r="F18" t="n">
-        <v>1.330087245640455</v>
+        <v>1.37722466829135</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0004300662056293536</v>
+        <v>-0.07259572896607258</v>
       </c>
       <c r="H18" t="n">
         <v>24</v>
@@ -907,7 +907,7 @@
         <v>45774</v>
       </c>
       <c r="B19" t="n">
-        <v>7.169525542715014</v>
+        <v>7.4307330575332</v>
       </c>
       <c r="C19" t="n">
         <v>24</v>
@@ -916,13 +916,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>2.327360416511448</v>
+        <v>2.426532749573146</v>
       </c>
       <c r="F19" t="n">
-        <v>3.377298541889068</v>
+        <v>3.476282607428775</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6459105349873684</v>
+        <v>0.6248506038148586</v>
       </c>
       <c r="H19" t="n">
         <v>24</v>
@@ -933,7 +933,7 @@
         <v>45775</v>
       </c>
       <c r="B20" t="n">
-        <v>5.561154578385461</v>
+        <v>5.547148036015994</v>
       </c>
       <c r="C20" t="n">
         <v>24</v>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>2.089713833333338</v>
+        <v>2.086755499650758</v>
       </c>
       <c r="F20" t="n">
-        <v>2.649464920946874</v>
+        <v>2.572451717735918</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.06540669299836743</v>
+        <v>-0.004369550289010204</v>
       </c>
       <c r="H20" t="n">
         <v>24</v>
@@ -959,7 +959,7 @@
         <v>45776</v>
       </c>
       <c r="B21" t="n">
-        <v>4.205753056260541</v>
+        <v>3.960742709161126</v>
       </c>
       <c r="C21" t="n">
         <v>24</v>
@@ -968,13 +968,13 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>1.631178583488555</v>
+        <v>1.533084250349248</v>
       </c>
       <c r="F21" t="n">
-        <v>2.006726343537488</v>
+        <v>1.950819151992832</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.08400718186835676</v>
+        <v>-0.02444790061719693</v>
       </c>
       <c r="H21" t="n">
         <v>24</v>
@@ -985,7 +985,7 @@
         <v>45777</v>
       </c>
       <c r="B22" t="n">
-        <v>3.744809449768428</v>
+        <v>3.796569073530175</v>
       </c>
       <c r="C22" t="n">
         <v>24</v>
@@ -994,13 +994,13 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>1.466188083333332</v>
+        <v>1.48927141631742</v>
       </c>
       <c r="F22" t="n">
-        <v>1.879323117944727</v>
+        <v>1.888283463712127</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.07422367126692375</v>
+        <v>-0.08449158287953895</v>
       </c>
       <c r="H22" t="n">
         <v>24</v>
@@ -1011,7 +1011,7 @@
         <v>45778</v>
       </c>
       <c r="B23" t="n">
-        <v>4.657733511802264</v>
+        <v>4.38411908387007</v>
       </c>
       <c r="C23" t="n">
         <v>24</v>
@@ -1020,13 +1020,13 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>1.749225000116416</v>
+        <v>1.640074999495535</v>
       </c>
       <c r="F23" t="n">
-        <v>2.124432789711926</v>
+        <v>2.049121362573408</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4299637968329321</v>
+        <v>0.4696631451057114</v>
       </c>
       <c r="H23" t="n">
         <v>24</v>
@@ -1037,7 +1037,7 @@
         <v>45779</v>
       </c>
       <c r="B24" t="n">
-        <v>3.298443527213569</v>
+        <v>3.239109138399784</v>
       </c>
       <c r="C24" t="n">
         <v>24</v>
@@ -1046,13 +1046,13 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>1.371793166860694</v>
+        <v>1.346555667171133</v>
       </c>
       <c r="F24" t="n">
-        <v>2.053164398017423</v>
+        <v>1.926808758172309</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.6884643031812745</v>
+        <v>-0.4870365967492785</v>
       </c>
       <c r="H24" t="n">
         <v>24</v>
@@ -1063,7 +1063,7 @@
         <v>45780</v>
       </c>
       <c r="B25" t="n">
-        <v>3.740742715376452</v>
+        <v>3.77859236603785</v>
       </c>
       <c r="C25" t="n">
         <v>24</v>
@@ -1072,13 +1072,13 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>1.51764375007761</v>
+        <v>1.530114582984087</v>
       </c>
       <c r="F25" t="n">
-        <v>1.79183705569869</v>
+        <v>1.826042242470769</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3975980201945701</v>
+        <v>0.374379453708778</v>
       </c>
       <c r="H25" t="n">
         <v>24</v>
@@ -1089,7 +1089,7 @@
         <v>45781</v>
       </c>
       <c r="B26" t="n">
-        <v>3.192861136718187</v>
+        <v>3.303278949025287</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
@@ -1098,13 +1098,13 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>1.346418916783083</v>
+        <v>1.391913249650754</v>
       </c>
       <c r="F26" t="n">
-        <v>1.647891810245564</v>
+        <v>1.701047277622942</v>
       </c>
       <c r="G26" t="n">
-        <v>0.03911045185882478</v>
+        <v>-0.02387949881709939</v>
       </c>
       <c r="H26" t="n">
         <v>24</v>
@@ -1115,7 +1115,7 @@
         <v>45782</v>
       </c>
       <c r="B27" t="n">
-        <v>2.249112793997005</v>
+        <v>2.467625510821925</v>
       </c>
       <c r="C27" t="n">
         <v>24</v>
@@ -1124,13 +1124,13 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0.99631875085371</v>
+        <v>1.09234941717113</v>
       </c>
       <c r="F27" t="n">
-        <v>1.199859344240207</v>
+        <v>1.274375393447676</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.8083729124401959</v>
+        <v>-1.039961971313915</v>
       </c>
       <c r="H27" t="n">
         <v>24</v>
@@ -1141,7 +1141,7 @@
         <v>45783</v>
       </c>
       <c r="B28" t="n">
-        <v>3.455122179725059</v>
+        <v>3.368874613636205</v>
       </c>
       <c r="C28" t="n">
         <v>24</v>
@@ -1150,13 +1150,13 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>1.449532762340024</v>
+        <v>1.414005082984088</v>
       </c>
       <c r="F28" t="n">
-        <v>1.868168637604633</v>
+        <v>1.86209401645364</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.5098460712478712</v>
+        <v>-0.5000430683828903</v>
       </c>
       <c r="H28" t="n">
         <v>24</v>
@@ -1167,7 +1167,7 @@
         <v>45784</v>
       </c>
       <c r="B29" t="n">
-        <v>3.397990121501965</v>
+        <v>3.338407251253999</v>
       </c>
       <c r="C29" t="n">
         <v>24</v>
@@ -1176,13 +1176,13 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>1.44057783376019</v>
+        <v>1.415109667171135</v>
       </c>
       <c r="F29" t="n">
-        <v>1.995634138941119</v>
+        <v>1.989766331551585</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.907879115387225</v>
+        <v>-0.8966760512572511</v>
       </c>
       <c r="H29" t="n">
         <v>24</v>
@@ -1193,7 +1193,7 @@
         <v>45785</v>
       </c>
       <c r="B30" t="n">
-        <v>3.338358895545156</v>
+        <v>3.430339727039366</v>
       </c>
       <c r="C30" t="n">
         <v>24</v>
@@ -1202,13 +1202,13 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>1.434915500232831</v>
+        <v>1.47452800050447</v>
       </c>
       <c r="F30" t="n">
-        <v>1.640436629495938</v>
+        <v>1.693674665599517</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.3210644197499433</v>
+        <v>-0.4082023417140688</v>
       </c>
       <c r="H30" t="n">
         <v>24</v>
@@ -1219,7 +1219,7 @@
         <v>45786</v>
       </c>
       <c r="B31" t="n">
-        <v>2.681473995527007</v>
+        <v>2.528796435449642</v>
       </c>
       <c r="C31" t="n">
         <v>24</v>
@@ -1228,13 +1228,13 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>1.162599999805975</v>
+        <v>1.098830667171135</v>
       </c>
       <c r="F31" t="n">
-        <v>1.456186861188088</v>
+        <v>1.422750251407675</v>
       </c>
       <c r="G31" t="n">
-        <v>0.4073737833199289</v>
+        <v>0.4342768048154239</v>
       </c>
       <c r="H31" t="n">
         <v>24</v>
@@ -1245,7 +1245,7 @@
         <v>45787</v>
       </c>
       <c r="B32" t="n">
-        <v>3.049258358261771</v>
+        <v>2.838869463827829</v>
       </c>
       <c r="C32" t="n">
         <v>24</v>
@@ -1254,13 +1254,13 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>1.270360583682582</v>
+        <v>1.182413250349247</v>
       </c>
       <c r="F32" t="n">
-        <v>1.455886960988094</v>
+        <v>1.412333622340443</v>
       </c>
       <c r="G32" t="n">
-        <v>-1.086711529660468</v>
+        <v>-0.9637296566836548</v>
       </c>
       <c r="H32" t="n">
         <v>24</v>
@@ -1271,7 +1271,7 @@
         <v>45788</v>
       </c>
       <c r="B33" t="n">
-        <v>3.736277134940089</v>
+        <v>3.646972542572038</v>
       </c>
       <c r="C33" t="n">
         <v>24</v>
@@ -1280,13 +1280,13 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>1.523643166511447</v>
+        <v>1.484585999495532</v>
       </c>
       <c r="F33" t="n">
-        <v>1.875857690786727</v>
+        <v>1.840272771566527</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2271360454776921</v>
+        <v>0.2561802986069774</v>
       </c>
       <c r="H33" t="n">
         <v>24</v>
@@ -1297,7 +1297,7 @@
         <v>45789</v>
       </c>
       <c r="B34" t="n">
-        <v>7.849023122630666</v>
+        <v>7.837172775873186</v>
       </c>
       <c r="C34" t="n">
         <v>24</v>
@@ -1306,13 +1306,13 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>2.822860416821888</v>
+        <v>2.816685416317422</v>
       </c>
       <c r="F34" t="n">
-        <v>4.283873624369394</v>
+        <v>4.234169516911761</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5789116907040472</v>
+        <v>0.5886264489607766</v>
       </c>
       <c r="H34" t="n">
         <v>24</v>
@@ -1323,7 +1323,7 @@
         <v>45790</v>
       </c>
       <c r="B35" t="n">
-        <v>3.149425500310383</v>
+        <v>3.152468189661806</v>
       </c>
       <c r="C35" t="n">
         <v>24</v>
@@ -1332,13 +1332,13 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>1.377426500543271</v>
+        <v>1.377176500349246</v>
       </c>
       <c r="F35" t="n">
-        <v>1.809257311884996</v>
+        <v>1.814556623112251</v>
       </c>
       <c r="G35" t="n">
-        <v>0.1059114417678823</v>
+        <v>0.1006662039805002</v>
       </c>
       <c r="H35" t="n">
         <v>24</v>
@@ -1349,7 +1349,7 @@
         <v>45791</v>
       </c>
       <c r="B36" t="n">
-        <v>3.45605416093562</v>
+        <v>3.291378863171082</v>
       </c>
       <c r="C36" t="n">
         <v>24</v>
@@ -1358,13 +1358,13 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>1.460902249961195</v>
+        <v>1.389313250349247</v>
       </c>
       <c r="F36" t="n">
-        <v>1.676219129104035</v>
+        <v>1.635312284685949</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.1168684521342345</v>
+        <v>-0.06302098289313451</v>
       </c>
       <c r="H36" t="n">
         <v>24</v>
@@ -1375,7 +1375,7 @@
         <v>45792</v>
       </c>
       <c r="B37" t="n">
-        <v>0.712101450020208</v>
+        <v>0.8873044299134455</v>
       </c>
       <c r="C37" t="n">
         <v>24</v>
@@ -1384,13 +1384,13 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>0.3048325826348404</v>
+        <v>0.3789027505044643</v>
       </c>
       <c r="F37" t="n">
-        <v>0.3678399234151236</v>
+        <v>0.4451684215797935</v>
       </c>
       <c r="G37" t="n">
-        <v>0.6658836629153579</v>
+        <v>0.5106397560840892</v>
       </c>
       <c r="H37" t="n">
         <v>24</v>
@@ -1401,7 +1401,7 @@
         <v>45793</v>
       </c>
       <c r="B38" t="n">
-        <v>2.746126919028864</v>
+        <v>2.975086691052327</v>
       </c>
       <c r="C38" t="n">
         <v>24</v>
@@ -1410,13 +1410,13 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>1.187393749961194</v>
+        <v>1.284825582984085</v>
       </c>
       <c r="F38" t="n">
-        <v>1.424373981505397</v>
+        <v>1.546364297732384</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.4751568933763162</v>
+        <v>-0.7386564559110267</v>
       </c>
       <c r="H38" t="n">
         <v>24</v>
@@ -1427,7 +1427,7 @@
         <v>45794</v>
       </c>
       <c r="B39" t="n">
-        <v>4.06115985269515</v>
+        <v>3.964730271584376</v>
       </c>
       <c r="C39" t="n">
         <v>24</v>
@@ -1436,13 +1436,13 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>1.78657441662786</v>
+        <v>1.745705082984086</v>
       </c>
       <c r="F39" t="n">
-        <v>2.106958318675141</v>
+        <v>2.097946913127796</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.1332619921895082</v>
+        <v>-0.1235888586696272</v>
       </c>
       <c r="H39" t="n">
         <v>24</v>
@@ -1453,7 +1453,7 @@
         <v>45795</v>
       </c>
       <c r="B40" t="n">
-        <v>3.227041053248969</v>
+        <v>3.288707575436273</v>
       </c>
       <c r="C40" t="n">
         <v>24</v>
@@ -1462,13 +1462,13 @@
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>1.42481250031044</v>
+        <v>1.45097916631742</v>
       </c>
       <c r="F40" t="n">
-        <v>1.739479506537115</v>
+        <v>1.7690138750026</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.333750022551819</v>
+        <v>-1.413671600974807</v>
       </c>
       <c r="H40" t="n">
         <v>24</v>
@@ -1479,7 +1479,7 @@
         <v>45796</v>
       </c>
       <c r="B41" t="n">
-        <v>3.994794829564805</v>
+        <v>3.896147161818443</v>
       </c>
       <c r="C41" t="n">
         <v>24</v>
@@ -1488,13 +1488,13 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>1.712629166821888</v>
+        <v>1.670859833682579</v>
       </c>
       <c r="F41" t="n">
-        <v>1.979136210986455</v>
+        <v>1.955829771761919</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0798865627429558</v>
+        <v>0.1014295990030425</v>
       </c>
       <c r="H41" t="n">
         <v>24</v>
@@ -1505,7 +1505,7 @@
         <v>45797</v>
       </c>
       <c r="B42" t="n">
-        <v>3.789011195801179</v>
+        <v>3.819735953033426</v>
       </c>
       <c r="C42" t="n">
         <v>24</v>
@@ -1514,13 +1514,13 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>1.7161187492239</v>
+        <v>1.731263083682579</v>
       </c>
       <c r="F42" t="n">
-        <v>2.254396588770756</v>
+        <v>2.292876094224265</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.2838128213642896</v>
+        <v>-0.3280127482732993</v>
       </c>
       <c r="H42" t="n">
         <v>24</v>
@@ -1531,7 +1531,7 @@
         <v>45798</v>
       </c>
       <c r="B43" t="n">
-        <v>3.03033487049331</v>
+        <v>2.943904819872214</v>
       </c>
       <c r="C43" t="n">
         <v>24</v>
@@ -1540,13 +1540,13 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>1.352481250077611</v>
+        <v>1.3155895838378</v>
       </c>
       <c r="F43" t="n">
-        <v>1.720805376652226</v>
+        <v>1.639347597659288</v>
       </c>
       <c r="G43" t="n">
-        <v>-1.150327250760731</v>
+        <v>-0.9515655683723601</v>
       </c>
       <c r="H43" t="n">
         <v>24</v>
@@ -1557,7 +1557,7 @@
         <v>45799</v>
       </c>
       <c r="B44" t="n">
-        <v>2.67464525457971</v>
+        <v>2.754315283268864</v>
       </c>
       <c r="C44" t="n">
         <v>24</v>
@@ -1566,13 +1566,13 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>1.161245250194025</v>
+        <v>1.195589583837798</v>
       </c>
       <c r="F44" t="n">
-        <v>1.377597574744319</v>
+        <v>1.409340381250901</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.06585585384096371</v>
+        <v>-0.1155409755322674</v>
       </c>
       <c r="H44" t="n">
         <v>24</v>
@@ -1583,7 +1583,7 @@
         <v>45800</v>
       </c>
       <c r="B45" t="n">
-        <v>4.999729283904869</v>
+        <v>5.048877714387693</v>
       </c>
       <c r="C45" t="n">
         <v>24</v>
@@ -1592,13 +1592,13 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>2.065521000232834</v>
+        <v>2.084114166317425</v>
       </c>
       <c r="F45" t="n">
-        <v>2.43489212206066</v>
+        <v>2.427584717092517</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.8406365908188866</v>
+        <v>-0.8296052240533507</v>
       </c>
       <c r="H45" t="n">
         <v>24</v>
@@ -1609,7 +1609,7 @@
         <v>45801</v>
       </c>
       <c r="B46" t="n">
-        <v>4.438819012156921</v>
+        <v>4.102247360783143</v>
       </c>
       <c r="C46" t="n">
         <v>24</v>
@@ -1618,13 +1618,13 @@
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>1.891240500232833</v>
+        <v>1.748498833682582</v>
       </c>
       <c r="F46" t="n">
-        <v>2.237150300167296</v>
+        <v>2.07056632953417</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.6876198854737627</v>
+        <v>-0.4456481467288262</v>
       </c>
       <c r="H46" t="n">
         <v>24</v>
@@ -1635,7 +1635,7 @@
         <v>45802</v>
       </c>
       <c r="B47" t="n">
-        <v>5.684404392470622</v>
+        <v>5.549911487428768</v>
       </c>
       <c r="C47" t="n">
         <v>24</v>
@@ -1644,13 +1644,13 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>2.205309666821886</v>
+        <v>2.151324833682578</v>
       </c>
       <c r="F47" t="n">
-        <v>2.956259995492076</v>
+        <v>2.881710747037658</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.1188244291237506</v>
+        <v>-0.06310818004263963</v>
       </c>
       <c r="H47" t="n">
         <v>24</v>
@@ -1661,7 +1661,7 @@
         <v>45803</v>
       </c>
       <c r="B48" t="n">
-        <v>2.691036921813511</v>
+        <v>2.871124629152781</v>
       </c>
       <c r="C48" t="n">
         <v>24</v>
@@ -1670,13 +1670,13 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>1.143541999999999</v>
+        <v>1.2196806661622</v>
       </c>
       <c r="F48" t="n">
-        <v>1.625276046223975</v>
+        <v>1.686401476050276</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.3293752372814294</v>
+        <v>-0.4312492192503736</v>
       </c>
       <c r="H48" t="n">
         <v>24</v>
@@ -1687,7 +1687,7 @@
         <v>45804</v>
       </c>
       <c r="B49" t="n">
-        <v>5.257908897509555</v>
+        <v>5.231073011975132</v>
       </c>
       <c r="C49" t="n">
         <v>24</v>
@@ -1696,13 +1696,13 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>2.14442633344975</v>
+        <v>2.130869499495536</v>
       </c>
       <c r="F49" t="n">
-        <v>2.524535826456853</v>
+        <v>2.54701640487157</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.007215894135151446</v>
+        <v>-0.02523394786712241</v>
       </c>
       <c r="H49" t="n">
         <v>24</v>
@@ -1713,7 +1713,7 @@
         <v>45805</v>
       </c>
       <c r="B50" t="n">
-        <v>3.792575222710973</v>
+        <v>3.843634466008</v>
       </c>
       <c r="C50" t="n">
         <v>24</v>
@@ -1722,13 +1722,13 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>1.69794241577415</v>
+        <v>1.719188250504465</v>
       </c>
       <c r="F50" t="n">
-        <v>2.40299511686207</v>
+        <v>2.477510742672656</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.1921359349197274</v>
+        <v>-0.2672173059329852</v>
       </c>
       <c r="H50" t="n">
         <v>24</v>
@@ -1739,7 +1739,7 @@
         <v>45806</v>
       </c>
       <c r="B51" t="n">
-        <v>3.844634052445678</v>
+        <v>3.925246292451839</v>
       </c>
       <c r="C51" t="n">
         <v>24</v>
@@ -1748,13 +1748,13 @@
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>1.612011749301512</v>
+        <v>1.646957582828871</v>
       </c>
       <c r="F51" t="n">
-        <v>2.119150693320071</v>
+        <v>2.209131670922202</v>
       </c>
       <c r="G51" t="n">
-        <v>0.7146977148202296</v>
+        <v>0.6899549708393815</v>
       </c>
       <c r="H51" t="n">
         <v>24</v>
@@ -1765,7 +1765,7 @@
         <v>45807</v>
       </c>
       <c r="B52" t="n">
-        <v>2.542933628983521</v>
+        <v>2.608960104232585</v>
       </c>
       <c r="C52" t="n">
         <v>24</v>
@@ -1774,13 +1774,13 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>1.123252082867675</v>
+        <v>1.151374416317424</v>
       </c>
       <c r="F52" t="n">
-        <v>1.505777661630401</v>
+        <v>1.561617720755505</v>
       </c>
       <c r="G52" t="n">
-        <v>0.7153214260928658</v>
+        <v>0.6938159673863822</v>
       </c>
       <c r="H52" t="n">
         <v>24</v>
@@ -1791,7 +1791,7 @@
         <v>45808</v>
       </c>
       <c r="B53" t="n">
-        <v>3.035613665392785</v>
+        <v>3.091030250662459</v>
       </c>
       <c r="C53" t="n">
         <v>24</v>
@@ -1800,13 +1800,13 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>1.351214582440821</v>
+        <v>1.376139583837804</v>
       </c>
       <c r="F53" t="n">
-        <v>1.68284685915204</v>
+        <v>1.72476025152066</v>
       </c>
       <c r="G53" t="n">
-        <v>0.5310027715377914</v>
+        <v>0.5073499251089483</v>
       </c>
       <c r="H53" t="n">
         <v>24</v>
@@ -1817,7 +1817,7 @@
         <v>45809</v>
       </c>
       <c r="B54" t="n">
-        <v>2.248782432805489</v>
+        <v>2.165577844417928</v>
       </c>
       <c r="C54" t="n">
         <v>24</v>
@@ -1826,13 +1826,13 @@
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>1.003691666278616</v>
+        <v>0.9657140003492467</v>
       </c>
       <c r="F54" t="n">
-        <v>1.288591776195979</v>
+        <v>1.32236716283926</v>
       </c>
       <c r="G54" t="n">
-        <v>0.6785859290874059</v>
+        <v>0.6615158888021719</v>
       </c>
       <c r="H54" t="n">
         <v>24</v>
@@ -1843,7 +1843,7 @@
         <v>45810</v>
       </c>
       <c r="B55" t="n">
-        <v>3.950046108941902</v>
+        <v>4.013261775410224</v>
       </c>
       <c r="C55" t="n">
         <v>24</v>
@@ -1852,13 +1852,13 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>1.67053808275126</v>
+        <v>1.69685208298409</v>
       </c>
       <c r="F55" t="n">
-        <v>2.616333310608777</v>
+        <v>2.679955894499124</v>
       </c>
       <c r="G55" t="n">
-        <v>0.3859983886448896</v>
+        <v>0.3557733848146007</v>
       </c>
       <c r="H55" t="n">
         <v>24</v>
@@ -1869,7 +1869,7 @@
         <v>45811</v>
       </c>
       <c r="B56" t="n">
-        <v>2.343189482735182</v>
+        <v>2.3966046600731</v>
       </c>
       <c r="C56" t="n">
         <v>24</v>
@@ -1878,13 +1878,13 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>1.05641874875824</v>
+        <v>1.079032749650759</v>
       </c>
       <c r="F56" t="n">
-        <v>1.411791836444903</v>
+        <v>1.483573096926739</v>
       </c>
       <c r="G56" t="n">
-        <v>0.7371799134180734</v>
+        <v>0.7097747994837771</v>
       </c>
       <c r="H56" t="n">
         <v>24</v>
@@ -1895,7 +1895,7 @@
         <v>45812</v>
       </c>
       <c r="B57" t="n">
-        <v>3.446326577719761</v>
+        <v>3.448660418238265</v>
       </c>
       <c r="C57" t="n">
         <v>24</v>
@@ -1904,13 +1904,13 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>1.431085416239813</v>
+        <v>1.438986917015913</v>
       </c>
       <c r="F57" t="n">
-        <v>2.1446801755452</v>
+        <v>2.152047225245238</v>
       </c>
       <c r="G57" t="n">
-        <v>0.6065624331896491</v>
+        <v>0.6038548478625019</v>
       </c>
       <c r="H57" t="n">
         <v>24</v>
@@ -1921,7 +1921,7 @@
         <v>45813</v>
       </c>
       <c r="B58" t="n">
-        <v>3.877524772609743</v>
+        <v>3.960343801943148</v>
       </c>
       <c r="C58" t="n">
         <v>24</v>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>1.671592416589058</v>
+        <v>1.707185583682578</v>
       </c>
       <c r="F58" t="n">
-        <v>2.030504022166203</v>
+        <v>2.024899269409899</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.08204521131330345</v>
+        <v>-0.07607996738040335</v>
       </c>
       <c r="H58" t="n">
         <v>24</v>
@@ -1947,7 +1947,7 @@
         <v>45814</v>
       </c>
       <c r="B59" t="n">
-        <v>2.583490267100641</v>
+        <v>2.679840959747066</v>
       </c>
       <c r="C59" t="n">
         <v>24</v>
@@ -1956,13 +1956,13 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>1.130961332790067</v>
+        <v>1.173969667171137</v>
       </c>
       <c r="F59" t="n">
-        <v>1.607627512830821</v>
+        <v>1.661240745480401</v>
       </c>
       <c r="G59" t="n">
-        <v>0.5407544427055493</v>
+        <v>0.5096126567282611</v>
       </c>
       <c r="H59" t="n">
         <v>24</v>
@@ -1973,7 +1973,7 @@
         <v>45815</v>
       </c>
       <c r="B60" t="n">
-        <v>2.550764282265684</v>
+        <v>2.485062057913891</v>
       </c>
       <c r="C60" t="n">
         <v>24</v>
@@ -1982,13 +1982,13 @@
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>1.174383332324404</v>
+        <v>1.144140166162202</v>
       </c>
       <c r="F60" t="n">
-        <v>1.451517040417554</v>
+        <v>1.444165451244063</v>
       </c>
       <c r="G60" t="n">
-        <v>-0.2908963180272712</v>
+        <v>-0.2778532651650096</v>
       </c>
       <c r="H60" t="n">
         <v>24</v>
@@ -1999,7 +1999,7 @@
         <v>45816</v>
       </c>
       <c r="B61" t="n">
-        <v>3.816670513550593</v>
+        <v>3.570501970043981</v>
       </c>
       <c r="C61" t="n">
         <v>24</v>
@@ -2008,13 +2008,13 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>1.626454916395035</v>
+        <v>1.52332575034925</v>
       </c>
       <c r="F61" t="n">
-        <v>2.012245473782427</v>
+        <v>1.914366341012978</v>
       </c>
       <c r="G61" t="n">
-        <v>0.5051865762441405</v>
+        <v>0.5521530155955963</v>
       </c>
       <c r="H61" t="n">
         <v>24</v>
@@ -2025,7 +2025,7 @@
         <v>45817</v>
       </c>
       <c r="B62" t="n">
-        <v>3.124114888382463</v>
+        <v>3.079785183653967</v>
       </c>
       <c r="C62" t="n">
         <v>24</v>
@@ -2034,13 +2034,13 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>1.36068141596818</v>
+        <v>1.342748082984092</v>
       </c>
       <c r="F62" t="n">
-        <v>1.707834458215035</v>
+        <v>1.721301470113588</v>
       </c>
       <c r="G62" t="n">
-        <v>0.6129938395721088</v>
+        <v>0.606866354260172</v>
       </c>
       <c r="H62" t="n">
         <v>24</v>
@@ -2051,7 +2051,7 @@
         <v>45818</v>
       </c>
       <c r="B63" t="n">
-        <v>3.154841190278717</v>
+        <v>3.17368295501712</v>
       </c>
       <c r="C63" t="n">
         <v>24</v>
@@ -2060,13 +2060,13 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>1.436940332557236</v>
+        <v>1.44655283298409</v>
       </c>
       <c r="F63" t="n">
-        <v>1.940816747335347</v>
+        <v>1.98468787568158</v>
       </c>
       <c r="G63" t="n">
-        <v>0.1345341423711915</v>
+        <v>0.09496513322287847</v>
       </c>
       <c r="H63" t="n">
         <v>24</v>
@@ -2077,7 +2077,7 @@
         <v>45819</v>
       </c>
       <c r="B64" t="n">
-        <v>4.289962916939861</v>
+        <v>4.304580606300745</v>
       </c>
       <c r="C64" t="n">
         <v>24</v>
@@ -2086,13 +2086,13 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>1.891943749456731</v>
+        <v>1.898839583837801</v>
       </c>
       <c r="F64" t="n">
-        <v>2.884685613321142</v>
+        <v>2.901884270764275</v>
       </c>
       <c r="G64" t="n">
-        <v>0.09445065383577356</v>
+        <v>0.08362059307920722</v>
       </c>
       <c r="H64" t="n">
         <v>24</v>
@@ -2103,7 +2103,7 @@
         <v>45820</v>
       </c>
       <c r="B65" t="n">
-        <v>3.388303572477569</v>
+        <v>3.401890429068082</v>
       </c>
       <c r="C65" t="n">
         <v>24</v>
@@ -2112,13 +2112,13 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>1.439485416278617</v>
+        <v>1.443836917015913</v>
       </c>
       <c r="F65" t="n">
-        <v>2.164905384785881</v>
+        <v>2.248933129396097</v>
       </c>
       <c r="G65" t="n">
-        <v>0.6534751705604259</v>
+        <v>0.6260533891986395</v>
       </c>
       <c r="H65" t="n">
         <v>24</v>
@@ -2129,7 +2129,7 @@
         <v>45821</v>
       </c>
       <c r="B66" t="n">
-        <v>5.113066326172429</v>
+        <v>4.978801416428175</v>
       </c>
       <c r="C66" t="n">
         <v>24</v>
@@ -2138,13 +2138,13 @@
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>2.151686166084595</v>
+        <v>2.09162100034925</v>
       </c>
       <c r="F66" t="n">
-        <v>2.696412952373367</v>
+        <v>2.694072019261685</v>
       </c>
       <c r="G66" t="n">
-        <v>0.4766296724473474</v>
+        <v>0.4775380222614704</v>
       </c>
       <c r="H66" t="n">
         <v>24</v>
@@ -2155,7 +2155,7 @@
         <v>45822</v>
       </c>
       <c r="B67" t="n">
-        <v>2.676482024062425</v>
+        <v>2.854996096304852</v>
       </c>
       <c r="C67" t="n">
         <v>24</v>
@@ -2164,13 +2164,13 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>1.146672916278617</v>
+        <v>1.220353582984089</v>
       </c>
       <c r="F67" t="n">
-        <v>1.807599626928957</v>
+        <v>1.912189063529325</v>
       </c>
       <c r="G67" t="n">
-        <v>0.7150662268663841</v>
+        <v>0.6811392208115964</v>
       </c>
       <c r="H67" t="n">
         <v>24</v>
@@ -2181,7 +2181,7 @@
         <v>45823</v>
       </c>
       <c r="B68" t="n">
-        <v>3.109612900984841</v>
+        <v>2.995186731940156</v>
       </c>
       <c r="C68" t="n">
         <v>24</v>
@@ -2190,13 +2190,13 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>1.368422916045789</v>
+        <v>1.319032750349249</v>
       </c>
       <c r="F68" t="n">
-        <v>1.755686141973096</v>
+        <v>1.795501161402512</v>
       </c>
       <c r="G68" t="n">
-        <v>0.6586360328306869</v>
+        <v>0.6429777394481682</v>
       </c>
       <c r="H68" t="n">
         <v>24</v>
@@ -2207,7 +2207,7 @@
         <v>45824</v>
       </c>
       <c r="B69" t="n">
-        <v>4.665148134802552</v>
+        <v>4.663282165780293</v>
       </c>
       <c r="C69" t="n">
         <v>24</v>
@@ -2216,13 +2216,13 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>1.904828999379121</v>
+        <v>1.904980500349249</v>
       </c>
       <c r="F69" t="n">
-        <v>2.528640042763177</v>
+        <v>2.530728595125577</v>
       </c>
       <c r="G69" t="n">
-        <v>0.6800377365617346</v>
+        <v>0.6795089670203031</v>
       </c>
       <c r="H69" t="n">
         <v>24</v>
@@ -2233,7 +2233,7 @@
         <v>45825</v>
       </c>
       <c r="B70" t="n">
-        <v>2.938680818298977</v>
+        <v>2.995338022572202</v>
       </c>
       <c r="C70" t="n">
         <v>24</v>
@@ -2242,13 +2242,13 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>1.282595999301514</v>
+        <v>1.306935000504472</v>
       </c>
       <c r="F70" t="n">
-        <v>1.803539315226413</v>
+        <v>1.871102465152688</v>
       </c>
       <c r="G70" t="n">
-        <v>0.552262744198726</v>
+        <v>0.5180886585966601</v>
       </c>
       <c r="H70" t="n">
         <v>24</v>
@@ -2259,7 +2259,7 @@
         <v>45826</v>
       </c>
       <c r="B71" t="n">
-        <v>2.815695807750537</v>
+        <v>2.779521147256199</v>
       </c>
       <c r="C71" t="n">
         <v>24</v>
@@ -2268,13 +2268,13 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>1.226936915968178</v>
+        <v>1.213111916162202</v>
       </c>
       <c r="F71" t="n">
-        <v>1.547251240330954</v>
+        <v>1.601303071462844</v>
       </c>
       <c r="G71" t="n">
-        <v>0.6383581998643441</v>
+        <v>0.6126495929590576</v>
       </c>
       <c r="H71" t="n">
         <v>24</v>
@@ -2285,7 +2285,7 @@
         <v>45827</v>
       </c>
       <c r="B72" t="n">
-        <v>3.613865684614574</v>
+        <v>3.629754412114476</v>
       </c>
       <c r="C72" t="n">
         <v>24</v>
@@ -2294,13 +2294,13 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>1.593881999650756</v>
+        <v>1.599061166317424</v>
       </c>
       <c r="F72" t="n">
-        <v>2.089474414888858</v>
+        <v>2.10093588143361</v>
       </c>
       <c r="G72" t="n">
-        <v>0.3600556680188063</v>
+        <v>0.3530157950795832</v>
       </c>
       <c r="H72" t="n">
         <v>24</v>
@@ -2311,7 +2311,7 @@
         <v>45828</v>
       </c>
       <c r="B73" t="n">
-        <v>3.24681395013473</v>
+        <v>3.27474336632534</v>
       </c>
       <c r="C73" t="n">
         <v>24</v>
@@ -2320,13 +2320,13 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1.365552665968178</v>
+        <v>1.377431832828869</v>
       </c>
       <c r="F73" t="n">
-        <v>1.936373037630922</v>
+        <v>2.029545368848515</v>
       </c>
       <c r="G73" t="n">
-        <v>0.7408975567347098</v>
+        <v>0.7153632429245071</v>
       </c>
       <c r="H73" t="n">
         <v>24</v>
@@ -2337,7 +2337,7 @@
         <v>45829</v>
       </c>
       <c r="B74" t="n">
-        <v>7.414968456734903</v>
+        <v>7.413221141668666</v>
       </c>
       <c r="C74" t="n">
         <v>24</v>
@@ -2346,13 +2346,13 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>2.847137499689563</v>
+        <v>2.842645833682583</v>
       </c>
       <c r="F74" t="n">
-        <v>4.621517510034995</v>
+        <v>4.612368275319527</v>
       </c>
       <c r="G74" t="n">
-        <v>0.3709704434191688</v>
+        <v>0.373458562228184</v>
       </c>
       <c r="H74" t="n">
         <v>24</v>
@@ -2363,7 +2363,7 @@
         <v>45830</v>
       </c>
       <c r="B75" t="n">
-        <v>9.384137202864846</v>
+        <v>9.422201960202607</v>
       </c>
       <c r="C75" t="n">
         <v>24</v>
@@ -2372,13 +2372,13 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>3.299495832906479</v>
+        <v>3.317745832984089</v>
       </c>
       <c r="F75" t="n">
-        <v>5.485396758321698</v>
+        <v>5.46594526324903</v>
       </c>
       <c r="G75" t="n">
-        <v>0.5209724196467396</v>
+        <v>0.5243637083094981</v>
       </c>
       <c r="H75" t="n">
         <v>24</v>
@@ -2389,7 +2389,7 @@
         <v>45831</v>
       </c>
       <c r="B76" t="n">
-        <v>4.183049434951469</v>
+        <v>4.05420057623431</v>
       </c>
       <c r="C76" t="n">
         <v>24</v>
@@ -2398,13 +2398,13 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>1.72015358344975</v>
+        <v>1.668413416317422</v>
       </c>
       <c r="F76" t="n">
-        <v>2.297726890483353</v>
+        <v>2.210769952405906</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.4728487226228679</v>
+        <v>-0.3634789428542444</v>
       </c>
       <c r="H76" t="n">
         <v>24</v>
@@ -2415,7 +2415,7 @@
         <v>45832</v>
       </c>
       <c r="B77" t="n">
-        <v>4.07610299372744</v>
+        <v>4.202409522243231</v>
       </c>
       <c r="C77" t="n">
         <v>24</v>
@@ -2424,13 +2424,13 @@
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>1.674434833333334</v>
+        <v>1.724866666162201</v>
       </c>
       <c r="F77" t="n">
-        <v>2.019787905021384</v>
+        <v>2.026654429225426</v>
       </c>
       <c r="G77" t="n">
-        <v>0.02460647024503804</v>
+        <v>0.01796325006316757</v>
       </c>
       <c r="H77" t="n">
         <v>24</v>
@@ -2441,7 +2441,7 @@
         <v>45833</v>
       </c>
       <c r="B78" t="n">
-        <v>2.662588982170119</v>
+        <v>2.624528485772109</v>
       </c>
       <c r="C78" t="n">
         <v>24</v>
@@ -2450,13 +2450,13 @@
         <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>1.236083332246796</v>
+        <v>1.21668750050447</v>
       </c>
       <c r="F78" t="n">
-        <v>1.548207577236941</v>
+        <v>1.558746270205859</v>
       </c>
       <c r="G78" t="n">
-        <v>-1.325660165640291</v>
+        <v>-1.357429596240118</v>
       </c>
       <c r="H78" t="n">
         <v>24</v>
@@ -2467,7 +2467,7 @@
         <v>45834</v>
       </c>
       <c r="B79" t="n">
-        <v>2.360160228877306</v>
+        <v>2.492624466341246</v>
       </c>
       <c r="C79" t="n">
         <v>24</v>
@@ -2476,13 +2476,13 @@
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>1.050512498991068</v>
+        <v>1.109464000504464</v>
       </c>
       <c r="F79" t="n">
-        <v>1.516987205149978</v>
+        <v>1.584477663240092</v>
       </c>
       <c r="G79" t="n">
-        <v>0.3407594196440576</v>
+        <v>0.2807955930678837</v>
       </c>
       <c r="H79" t="n">
         <v>24</v>
@@ -2493,7 +2493,7 @@
         <v>45835</v>
       </c>
       <c r="B80" t="n">
-        <v>4.006033310928208</v>
+        <v>3.821524536715495</v>
       </c>
       <c r="C80" t="n">
         <v>24</v>
@@ -2502,13 +2502,13 @@
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>1.733126500116415</v>
+        <v>1.6522958338378</v>
       </c>
       <c r="F80" t="n">
-        <v>2.186716121377954</v>
+        <v>2.087441680357113</v>
       </c>
       <c r="G80" t="n">
-        <v>0.0006167478468468435</v>
+        <v>0.08929870237845683</v>
       </c>
       <c r="H80" t="n">
         <v>24</v>
@@ -2519,7 +2519,7 @@
         <v>45836</v>
       </c>
       <c r="B81" t="n">
-        <v>3.036631675124819</v>
+        <v>3.042430633471173</v>
       </c>
       <c r="C81" t="n">
         <v>24</v>
@@ -2528,13 +2528,13 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>1.330958332984089</v>
+        <v>1.333245832828866</v>
       </c>
       <c r="F81" t="n">
-        <v>1.629178236756921</v>
+        <v>1.627212744462809</v>
       </c>
       <c r="G81" t="n">
-        <v>0.3034904785609573</v>
+        <v>0.3051700471598749</v>
       </c>
       <c r="H81" t="n">
         <v>24</v>
@@ -2545,7 +2545,7 @@
         <v>45837</v>
       </c>
       <c r="B82" t="n">
-        <v>3.104774915803854</v>
+        <v>3.216403012583378</v>
       </c>
       <c r="C82" t="n">
         <v>24</v>
@@ -2554,13 +2554,13 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>1.410358332634843</v>
+        <v>1.459062500504467</v>
       </c>
       <c r="F82" t="n">
-        <v>1.764518794401635</v>
+        <v>1.812641109507148</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.2934807747489876</v>
+        <v>-0.3649949719524435</v>
       </c>
       <c r="H82" t="n">
         <v>24</v>
@@ -2571,7 +2571,7 @@
         <v>45838</v>
       </c>
       <c r="B83" t="n">
-        <v>3.818746560884607</v>
+        <v>3.845142983759466</v>
       </c>
       <c r="C83" t="n">
         <v>23</v>
@@ -2580,13 +2580,13 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>1.610600782608698</v>
+        <v>1.629081217917704</v>
       </c>
       <c r="F83" t="n">
-        <v>2.561816290986406</v>
+        <v>2.538714201969651</v>
       </c>
       <c r="G83" t="n">
-        <v>0.5232849605693957</v>
+        <v>0.5318440879223618</v>
       </c>
       <c r="H83" t="n">
         <v>23</v>
